--- a/Psion Levels.xlsx
+++ b/Psion Levels.xlsx
@@ -8,17 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Zak\Documents\GitProjects\psion3d\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E10F7E9C-949B-44C6-9636-11D3D0F90EF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AD41139-157D-48AC-8623-2A0220C1B26C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{72A343FB-71F0-4738-BBFF-B23B40D170FF}"/>
   </bookViews>
   <sheets>
     <sheet name="Mapbits" sheetId="4" r:id="rId1"/>
-    <sheet name="Tiles Type" sheetId="2" r:id="rId2"/>
-    <sheet name="Level 1" sheetId="1" r:id="rId3"/>
-    <sheet name="Memory Budget" sheetId="3" r:id="rId4"/>
-    <sheet name="Performance" sheetId="6" r:id="rId5"/>
-    <sheet name="Optimisation" sheetId="7" r:id="rId6"/>
+    <sheet name="Sheet1" sheetId="8" r:id="rId2"/>
+    <sheet name="Tiles Type" sheetId="2" r:id="rId3"/>
+    <sheet name="Level 1" sheetId="1" r:id="rId4"/>
+    <sheet name="Memory Budget" sheetId="3" r:id="rId5"/>
+    <sheet name="Performance" sheetId="6" r:id="rId6"/>
+    <sheet name="Optimisation" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4128" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4181" uniqueCount="86">
   <si>
     <t>X</t>
   </si>
@@ -227,6 +228,81 @@
   </si>
   <si>
     <t>Sprite Load</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>Fodder enemy</t>
+  </si>
+  <si>
+    <t>Mid Enemy</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>Heavy Enetmy</t>
+  </si>
+  <si>
+    <t>Civilian</t>
+  </si>
+  <si>
+    <t>Sprite Frames</t>
+  </si>
+  <si>
+    <t>States</t>
+  </si>
+  <si>
+    <t>Idle.</t>
+  </si>
+  <si>
+    <t>Searching.</t>
+  </si>
+  <si>
+    <t>Chasing.</t>
+  </si>
+  <si>
+    <t>Attacking.</t>
+  </si>
+  <si>
+    <t>Stay put</t>
+  </si>
+  <si>
+    <t>Walk randomly</t>
+  </si>
+  <si>
+    <t>Walk to player</t>
+  </si>
+  <si>
+    <t>Shoot</t>
+  </si>
+  <si>
+    <t>Shoot when line of sight.</t>
+  </si>
+  <si>
+    <t>Store last seen point, go there. If can't see player anymore, go to searching.</t>
+  </si>
+  <si>
+    <t>Check player LOS. Go to chase when seen</t>
+  </si>
+  <si>
+    <t>Stand</t>
+  </si>
+  <si>
+    <t>Walk 1</t>
+  </si>
+  <si>
+    <t>Walk 2</t>
+  </si>
+  <si>
+    <t>Aim</t>
+  </si>
+  <si>
+    <t>Ouch</t>
   </si>
 </sst>
 </file>
@@ -797,199 +873,82 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3F90467-4CD9-40FD-80C5-3B27CEDF7551}">
-  <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1F75B1B-87D7-4382-913C-AEB74E49A06D}">
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="68" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B1" t="s">
-        <v>8</v>
+      <c r="A1" t="s">
+        <v>68</v>
       </c>
       <c r="C1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E1" t="s">
-        <v>29</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="3">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>16</v>
+      <c r="A2" t="s">
+        <v>81</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E2" t="s">
-        <v>27</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" t="s">
-        <v>9</v>
+      <c r="A3" t="s">
+        <v>82</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>75</v>
       </c>
       <c r="E3" t="s">
-        <v>26</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
+      <c r="A4" t="s">
+        <v>83</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>72</v>
       </c>
       <c r="D4" t="s">
-        <v>27</v>
+        <v>76</v>
       </c>
       <c r="E4" t="s">
-        <v>26</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" t="s">
-        <v>11</v>
+      <c r="A5" t="s">
+        <v>84</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>73</v>
       </c>
       <c r="D5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E5" t="s">
-        <v>26</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6" t="s">
-        <v>27</v>
+      <c r="A6" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" t="s">
-        <v>27</v>
-      </c>
-      <c r="E9" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" t="s">
-        <v>26</v>
-      </c>
-      <c r="D10" t="s">
-        <v>27</v>
-      </c>
-      <c r="E10" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" t="s">
-        <v>27</v>
-      </c>
-      <c r="D11" t="s">
-        <v>27</v>
-      </c>
-      <c r="E11" t="s">
-        <v>26</v>
+      <c r="A7" t="s">
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -998,6 +957,320 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3F90467-4CD9-40FD-80C5-3B27CEDF7551}">
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="6.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" t="s">
+        <v>26</v>
+      </c>
+      <c r="F10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B13" t="s">
+        <v>62</v>
+      </c>
+      <c r="C13" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" t="s">
+        <v>26</v>
+      </c>
+      <c r="E13" t="s">
+        <v>27</v>
+      </c>
+      <c r="F13" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B14" t="s">
+        <v>63</v>
+      </c>
+      <c r="C14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D14" t="s">
+        <v>26</v>
+      </c>
+      <c r="E14" t="s">
+        <v>27</v>
+      </c>
+      <c r="F14" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B15" t="s">
+        <v>66</v>
+      </c>
+      <c r="C15" t="s">
+        <v>26</v>
+      </c>
+      <c r="D15" t="s">
+        <v>26</v>
+      </c>
+      <c r="E15" t="s">
+        <v>27</v>
+      </c>
+      <c r="F15" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B16" t="s">
+        <v>67</v>
+      </c>
+      <c r="C16" t="s">
+        <v>26</v>
+      </c>
+      <c r="D16" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" t="s">
+        <v>27</v>
+      </c>
+      <c r="F16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{750D9AD9-7C84-4603-A2EE-1597D412FCF4}">
   <dimension ref="A1:BP64"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -14414,7 +14687,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE5E0410-6B34-4610-813C-474405B474F7}">
   <dimension ref="A2:D12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -14510,7 +14783,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{692BE518-AAC1-41EE-AD19-DC91CDF8547C}">
   <dimension ref="A1:L4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -14630,7 +14903,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB40D263-C04C-4263-859C-02DFCB83777C}">
   <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/Psion Levels.xlsx
+++ b/Psion Levels.xlsx
@@ -8,18 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Zak\Documents\GitProjects\psion3d\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AD41139-157D-48AC-8623-2A0220C1B26C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCDCC05D-4E99-4D0A-A723-5120B179CB81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{72A343FB-71F0-4738-BBFF-B23B40D170FF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{72A343FB-71F0-4738-BBFF-B23B40D170FF}"/>
   </bookViews>
   <sheets>
     <sheet name="Mapbits" sheetId="4" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="8" r:id="rId2"/>
-    <sheet name="Tiles Type" sheetId="2" r:id="rId3"/>
-    <sheet name="Level 1" sheetId="1" r:id="rId4"/>
-    <sheet name="Memory Budget" sheetId="3" r:id="rId5"/>
-    <sheet name="Performance" sheetId="6" r:id="rId6"/>
-    <sheet name="Optimisation" sheetId="7" r:id="rId7"/>
+    <sheet name="Sheet2" sheetId="9" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="8" r:id="rId3"/>
+    <sheet name="Tiles Type" sheetId="2" r:id="rId4"/>
+    <sheet name="Level 1" sheetId="1" r:id="rId5"/>
+    <sheet name="Memory Budget" sheetId="3" r:id="rId6"/>
+    <sheet name="Performance" sheetId="6" r:id="rId7"/>
+    <sheet name="Optimisation" sheetId="7" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4181" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4189" uniqueCount="92">
   <si>
     <t>X</t>
   </si>
@@ -293,16 +294,34 @@
     <t>Stand</t>
   </si>
   <si>
-    <t>Walk 1</t>
-  </si>
-  <si>
-    <t>Walk 2</t>
-  </si>
-  <si>
     <t>Aim</t>
   </si>
   <si>
     <t>Ouch</t>
+  </si>
+  <si>
+    <t>Sprite Slots</t>
+  </si>
+  <si>
+    <t>Mercenary</t>
+  </si>
+  <si>
+    <t>Solgier</t>
+  </si>
+  <si>
+    <t>Heavy</t>
+  </si>
+  <si>
+    <t>Walk R 1</t>
+  </si>
+  <si>
+    <t>Walk R 2</t>
+  </si>
+  <si>
+    <t>Walk L 1</t>
+  </si>
+  <si>
+    <t>Walk L 2</t>
   </si>
 </sst>
 </file>
@@ -873,82 +892,48 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1F75B1B-87D7-4382-913C-AEB74E49A06D}">
-  <dimension ref="A1:E7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5235E873-4701-4130-881C-1F333236149A}">
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="68" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D2" t="s">
-        <v>74</v>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>82</v>
-      </c>
-      <c r="C3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D3" t="s">
-        <v>75</v>
-      </c>
-      <c r="E3" t="s">
-        <v>80</v>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>85</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>83</v>
-      </c>
-      <c r="C4" t="s">
-        <v>72</v>
-      </c>
-      <c r="D4" t="s">
-        <v>76</v>
-      </c>
-      <c r="E4" t="s">
-        <v>79</v>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>86</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>84</v>
-      </c>
-      <c r="C5" t="s">
-        <v>73</v>
-      </c>
-      <c r="D5" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>85</v>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -957,6 +942,125 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1F75B1B-87D7-4382-913C-AEB74E49A06D}">
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="68" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D3" t="s">
+        <v>71</v>
+      </c>
+      <c r="E3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>90</v>
+      </c>
+      <c r="D5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E5" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3F90467-4CD9-40FD-80C5-3B27CEDF7551}">
   <dimension ref="A1:F16"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
@@ -1270,7 +1374,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{750D9AD9-7C84-4603-A2EE-1597D412FCF4}">
   <dimension ref="A1:BP64"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -14687,7 +14791,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE5E0410-6B34-4610-813C-474405B474F7}">
   <dimension ref="A2:D12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -14783,7 +14887,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{692BE518-AAC1-41EE-AD19-DC91CDF8547C}">
   <dimension ref="A1:L4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -14903,9 +15007,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB40D263-C04C-4263-859C-02DFCB83777C}">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
@@ -14947,15 +15051,15 @@
         <v>140</v>
       </c>
       <c r="C3" s="4">
-        <f t="shared" ref="C3:C8" si="0">(B3/$B$2)-1</f>
+        <f t="shared" ref="C3:C9" si="0">(B3/$B$2)-1</f>
         <v>7.6923076923076872E-2</v>
       </c>
       <c r="E3">
-        <f t="shared" ref="E3:E8" si="1">B3/40</f>
+        <f t="shared" ref="E3:E9" si="1">B3/40</f>
         <v>3.5</v>
       </c>
       <c r="F3">
-        <f t="shared" ref="F3:F8" si="2">E3/3</f>
+        <f t="shared" ref="F3:F9" si="2">E3/3</f>
         <v>1.1666666666666667</v>
       </c>
     </row>
@@ -15057,6 +15161,26 @@
       <c r="F8">
         <f t="shared" si="2"/>
         <v>4.416666666666667</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>55</v>
+      </c>
+      <c r="B9">
+        <v>570</v>
+      </c>
+      <c r="C9" s="4">
+        <f t="shared" si="0"/>
+        <v>3.384615384615385</v>
+      </c>
+      <c r="E9">
+        <f t="shared" si="1"/>
+        <v>14.25</v>
+      </c>
+      <c r="F9">
+        <f t="shared" si="2"/>
+        <v>4.75</v>
       </c>
     </row>
   </sheetData>

--- a/Psion Levels.xlsx
+++ b/Psion Levels.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Zak\Documents\GitProjects\psion3d\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FC00CAD-7611-4AA1-8E08-772A3A7DCA30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{324A20A8-1F1D-497D-BA11-3D9E1746D0E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{72A343FB-71F0-4738-BBFF-B23B40D170FF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{72A343FB-71F0-4738-BBFF-B23B40D170FF}"/>
   </bookViews>
   <sheets>
     <sheet name="Mapbits" sheetId="4" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4189" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4204" uniqueCount="92">
   <si>
     <t>X</t>
   </si>
@@ -147,9 +147,6 @@
     <t>Sprite</t>
   </si>
   <si>
-    <t>Id</t>
-  </si>
-  <si>
     <t>Bit</t>
   </si>
   <si>
@@ -166,9 +163,6 @@
   </si>
   <si>
     <t>Set when this cell contains a renderable wall</t>
-  </si>
-  <si>
-    <t>Id of block/sprite etc so up to 8 types of wall/sprite etc.</t>
   </si>
   <si>
     <t>Emu</t>
@@ -323,6 +317,12 @@
   <si>
     <t>Walk L 2</t>
   </si>
+  <si>
+    <t>Enemy</t>
+  </si>
+  <si>
+    <t>Block contains an enemy.</t>
+  </si>
 </sst>
 </file>
 
@@ -372,7 +372,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -382,9 +382,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -781,7 +778,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A21D89A8-E5EC-4EAA-92CE-B056DD4B8657}">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.5703125" bestFit="1" customWidth="1"/>
@@ -796,7 +793,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B1" t="s">
         <v>8</v>
@@ -804,89 +801,121 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
         <v>30</v>
       </c>
       <c r="C2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
         <v>32</v>
       </c>
       <c r="C3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
         <v>28</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
         <v>31</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>2</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>40</v>
+        <v>10</v>
+      </c>
+      <c r="B7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C7" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>1</v>
-      </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
+        <v>9</v>
+      </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>0</v>
-      </c>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="C7:C9"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -901,7 +930,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -909,7 +938,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -917,7 +946,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -925,7 +954,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -933,7 +962,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -955,10 +984,10 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -966,13 +995,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -980,16 +1009,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -997,16 +1026,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -1014,13 +1043,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -1028,7 +1057,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -1036,7 +1065,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -1044,7 +1073,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -1052,7 +1081,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -1062,14 +1091,14 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3F90467-4CD9-40FD-80C5-3B27CEDF7551}">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>7</v>
       </c>
@@ -1088,8 +1117,11 @@
       <c r="F1" t="s">
         <v>32</v>
       </c>
+      <c r="G1" t="s">
+        <v>90</v>
+      </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>0</v>
       </c>
@@ -1108,8 +1140,11 @@
       <c r="F2" t="s">
         <v>26</v>
       </c>
+      <c r="G2" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
@@ -1128,8 +1163,11 @@
       <c r="F3" t="s">
         <v>26</v>
       </c>
+      <c r="G3" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
@@ -1148,8 +1186,11 @@
       <c r="F4" t="s">
         <v>26</v>
       </c>
+      <c r="G4" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>1</v>
       </c>
@@ -1168,8 +1209,11 @@
       <c r="F5" t="s">
         <v>26</v>
       </c>
+      <c r="G5" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>2</v>
       </c>
@@ -1188,8 +1232,11 @@
       <c r="F6" t="s">
         <v>26</v>
       </c>
+      <c r="G6" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>3</v>
       </c>
@@ -1208,8 +1255,11 @@
       <c r="F7" t="s">
         <v>26</v>
       </c>
+      <c r="G7" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>6</v>
       </c>
@@ -1228,8 +1278,11 @@
       <c r="F8" t="s">
         <v>27</v>
       </c>
+      <c r="G8" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>5</v>
       </c>
@@ -1248,8 +1301,11 @@
       <c r="F9" t="s">
         <v>26</v>
       </c>
+      <c r="G9" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>21</v>
       </c>
@@ -1268,8 +1324,11 @@
       <c r="F10" t="s">
         <v>26</v>
       </c>
+      <c r="G10" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>23</v>
       </c>
@@ -1288,13 +1347,16 @@
       <c r="F11" t="s">
         <v>26</v>
       </c>
+      <c r="G11" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B13" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C13" t="s">
         <v>26</v>
@@ -1308,13 +1370,16 @@
       <c r="F13" t="s">
         <v>27</v>
       </c>
+      <c r="G13" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B14" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C14" t="s">
         <v>26</v>
@@ -1328,13 +1393,16 @@
       <c r="F14" t="s">
         <v>27</v>
       </c>
+      <c r="G14" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B15" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C15" t="s">
         <v>26</v>
@@ -1348,13 +1416,16 @@
       <c r="F15" t="s">
         <v>27</v>
       </c>
+      <c r="G15" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B16" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C16" t="s">
         <v>26</v>
@@ -1366,6 +1437,9 @@
         <v>27</v>
       </c>
       <c r="F16" t="s">
+        <v>27</v>
+      </c>
+      <c r="G16" t="s">
         <v>27</v>
       </c>
     </row>
@@ -14819,7 +14893,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B4">
         <f>2*1024</f>
@@ -14828,7 +14902,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B5">
         <f>8*1024</f>
@@ -14837,7 +14911,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B6">
         <f>HEX2DEC("2000")</f>
@@ -14846,7 +14920,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B7">
         <v>4096</v>
@@ -14854,7 +14928,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B8">
         <v>1024</v>
@@ -14897,30 +14971,30 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1" t="s">
         <v>45</v>
-      </c>
-      <c r="F1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G1" t="s">
-        <v>46</v>
-      </c>
-      <c r="H1" t="s">
-        <v>45</v>
-      </c>
-      <c r="J1" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B2">
         <v>16</v>
@@ -14947,7 +15021,7 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B3">
         <v>640</v>
@@ -14977,7 +15051,7 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B4">
         <v>20</v>
@@ -15018,18 +15092,18 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B2">
         <v>130</v>
@@ -15045,7 +15119,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B3">
         <v>140</v>
@@ -15065,7 +15139,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B4">
         <v>360</v>
@@ -15085,7 +15159,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B5">
         <v>360</v>
@@ -15105,7 +15179,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B6">
         <v>630</v>
@@ -15125,7 +15199,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B7">
         <v>410</v>
@@ -15145,7 +15219,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B8">
         <v>530</v>
@@ -15165,7 +15239,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B9">
         <v>570</v>

--- a/Psion Levels.xlsx
+++ b/Psion Levels.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Zak\Documents\GitProjects\psion3d\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{324A20A8-1F1D-497D-BA11-3D9E1746D0E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC656820-2D20-43AE-86B5-3FB7D5DA0A0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{72A343FB-71F0-4738-BBFF-B23B40D170FF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{72A343FB-71F0-4738-BBFF-B23B40D170FF}"/>
   </bookViews>
   <sheets>
     <sheet name="Mapbits" sheetId="4" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="9" r:id="rId2"/>
-    <sheet name="Sheet1" sheetId="8" r:id="rId3"/>
+    <sheet name="AI States" sheetId="8" r:id="rId3"/>
     <sheet name="Tiles Type" sheetId="2" r:id="rId4"/>
     <sheet name="Level 1" sheetId="1" r:id="rId5"/>
     <sheet name="Memory Budget" sheetId="3" r:id="rId6"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4204" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4227" uniqueCount="101">
   <si>
     <t>X</t>
   </si>
@@ -64,9 +64,6 @@
   </si>
   <si>
     <t>S</t>
-  </si>
-  <si>
-    <t>H</t>
   </si>
   <si>
     <t>Type</t>
@@ -88,9 +85,6 @@
   </si>
   <si>
     <t>Unlocked Door</t>
-  </si>
-  <si>
-    <t>Health Pack</t>
   </si>
   <si>
     <t>Secret Wall</t>
@@ -145,6 +139,9 @@
   </si>
   <si>
     <t>Sprite</t>
+  </si>
+  <si>
+    <t>Id</t>
   </si>
   <si>
     <t>Bit</t>
@@ -228,19 +225,10 @@
     <t>E</t>
   </si>
   <si>
-    <t>Fodder enemy</t>
-  </si>
-  <si>
-    <t>Mid Enemy</t>
-  </si>
-  <si>
     <t>F</t>
   </si>
   <si>
     <t>G</t>
-  </si>
-  <si>
-    <t>Heavy Enetmy</t>
   </si>
   <si>
     <t>Civilian</t>
@@ -323,6 +311,45 @@
   <si>
     <t>Block contains an enemy.</t>
   </si>
+  <si>
+    <t>Game Seg</t>
+  </si>
+  <si>
+    <t>Other Segs</t>
+  </si>
+  <si>
+    <t>Mercenary enemy</t>
+  </si>
+  <si>
+    <t>Soldier Enemy</t>
+  </si>
+  <si>
+    <t>Heavy Enemy</t>
+  </si>
+  <si>
+    <t>Wall types</t>
+  </si>
+  <si>
+    <t>Default wall</t>
+  </si>
+  <si>
+    <t>Dark Wall</t>
+  </si>
+  <si>
+    <t>Bars</t>
+  </si>
+  <si>
+    <t>Enemy Types</t>
+  </si>
+  <si>
+    <t>Soldier</t>
+  </si>
+  <si>
+    <t>Bitmask maps</t>
+  </si>
+  <si>
+    <t>U16 map</t>
+  </si>
 </sst>
 </file>
 
@@ -372,7 +399,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -382,11 +409,107 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFF00"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -778,7 +901,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A21D89A8-E5EC-4EAA-92CE-B056DD4B8657}">
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.5703125" bestFit="1" customWidth="1"/>
@@ -789,134 +912,326 @@
     <col min="6" max="6" width="9.85546875" customWidth="1"/>
     <col min="7" max="7" width="11" customWidth="1"/>
     <col min="8" max="8" width="13" customWidth="1"/>
+    <col min="9" max="9" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B1" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="F1" t="s">
+        <v>93</v>
+      </c>
+      <c r="G1">
+        <v>0</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="I1" t="s">
+        <v>94</v>
+      </c>
+      <c r="K1" t="s">
+        <v>97</v>
+      </c>
+      <c r="L1">
+        <v>0</v>
+      </c>
+      <c r="M1" t="s">
+        <v>61</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C2" t="s">
-        <v>34</v>
+        <v>33</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I2" t="s">
+        <v>95</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2" t="s">
+        <v>79</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s">
         <v>35</v>
       </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="I3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3" t="s">
+        <v>98</v>
+      </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="G4">
+        <v>3</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I4" t="s">
+        <v>11</v>
+      </c>
+      <c r="L4">
+        <v>3</v>
+      </c>
+      <c r="M4" t="s">
+        <v>81</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>34</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I5" t="s">
+        <v>12</v>
+      </c>
+      <c r="L5">
+        <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>31</v>
+        <v>86</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>87</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I6" t="s">
+        <v>13</v>
+      </c>
+      <c r="L6">
+        <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>91</v>
+        <v>36</v>
+      </c>
+      <c r="G7">
+        <v>6</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I7" t="s">
+        <v>96</v>
+      </c>
+      <c r="L7">
+        <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>9</v>
       </c>
+      <c r="B8" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="G8">
+        <v>7</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L8">
+        <v>7</v>
+      </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
+      <c r="B9" s="6"/>
+      <c r="G9">
+        <v>8</v>
+      </c>
+      <c r="L9">
+        <v>8</v>
+      </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>7</v>
       </c>
+      <c r="B10" s="6"/>
+      <c r="C10" s="7"/>
+      <c r="G10">
+        <v>9</v>
+      </c>
+      <c r="L10">
+        <v>9</v>
+      </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>6</v>
       </c>
+      <c r="B11" s="6"/>
+      <c r="C11" s="7"/>
+      <c r="G11">
+        <v>10</v>
+      </c>
+      <c r="L11">
+        <v>10</v>
+      </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>5</v>
       </c>
+      <c r="B12" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="7"/>
+      <c r="G12">
+        <v>11</v>
+      </c>
+      <c r="L12">
+        <v>11</v>
+      </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>4</v>
       </c>
+      <c r="B13" s="6"/>
+      <c r="C13" s="7"/>
+      <c r="G13">
+        <v>12</v>
+      </c>
+      <c r="L13">
+        <v>12</v>
+      </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>3</v>
       </c>
+      <c r="B14" s="6"/>
+      <c r="C14" s="7"/>
+      <c r="G14">
+        <v>13</v>
+      </c>
+      <c r="L14">
+        <v>13</v>
+      </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2</v>
       </c>
+      <c r="B15" s="6"/>
+      <c r="C15" s="7"/>
+      <c r="G15">
+        <v>14</v>
+      </c>
+      <c r="L15">
+        <v>14</v>
+      </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>1</v>
       </c>
+      <c r="B16" s="6"/>
+      <c r="C16" s="7"/>
+      <c r="G16">
+        <v>15</v>
+      </c>
+      <c r="L16">
+        <v>15</v>
+      </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>0</v>
       </c>
+      <c r="B17" s="6"/>
+      <c r="C17" s="7"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B8:B11"/>
+    <mergeCell ref="B12:B17"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -930,7 +1245,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -938,7 +1253,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -946,7 +1261,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -954,7 +1269,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -962,7 +1277,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -984,10 +1299,10 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -995,13 +1310,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2" t="s">
         <v>68</v>
-      </c>
-      <c r="E2" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -1009,16 +1324,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E3" t="s">
         <v>69</v>
       </c>
-      <c r="E3" t="s">
-        <v>73</v>
-      </c>
       <c r="F3" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1026,16 +1341,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E4" t="s">
         <v>70</v>
       </c>
-      <c r="E4" t="s">
-        <v>74</v>
-      </c>
       <c r="F4" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -1043,13 +1358,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D5" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="E5" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -1057,7 +1372,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -1065,7 +1380,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -1073,7 +1388,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -1081,7 +1396,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -1091,34 +1406,34 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3F90467-4CD9-40FD-80C5-3B27CEDF7551}">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
         <v>7</v>
       </c>
-      <c r="B1" t="s">
-        <v>8</v>
-      </c>
       <c r="C1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -1126,22 +1441,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -1149,22 +1464,22 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1172,22 +1487,22 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -1195,22 +1510,22 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -1218,22 +1533,22 @@
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -1241,68 +1556,68 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F8" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G8" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D9" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E9" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F9" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G9" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -1313,42 +1628,42 @@
         <v>22</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D10" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E10" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F10" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G10" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" t="s">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B12" t="s">
+        <v>90</v>
+      </c>
+      <c r="C12" t="s">
         <v>24</v>
       </c>
-      <c r="C11" t="s">
-        <v>27</v>
-      </c>
-      <c r="D11" t="s">
-        <v>27</v>
-      </c>
-      <c r="E11" t="s">
-        <v>26</v>
-      </c>
-      <c r="F11" t="s">
-        <v>26</v>
-      </c>
-      <c r="G11" t="s">
-        <v>26</v>
+      <c r="D12" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" t="s">
+        <v>25</v>
+      </c>
+      <c r="G12" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -1356,110 +1671,86 @@
         <v>59</v>
       </c>
       <c r="B13" t="s">
-        <v>60</v>
+        <v>91</v>
       </c>
       <c r="C13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B14" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="C14" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D14" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E14" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F14" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G14" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="B15" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C15" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D15" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E15" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F15" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G15" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B16" t="s">
-        <v>65</v>
-      </c>
-      <c r="C16" t="s">
-        <v>26</v>
-      </c>
-      <c r="D16" t="s">
-        <v>26</v>
-      </c>
-      <c r="E16" t="s">
-        <v>27</v>
-      </c>
-      <c r="F16" t="s">
-        <v>27</v>
-      </c>
-      <c r="G16" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{750D9AD9-7C84-4603-A2EE-1597D412FCF4}">
-  <dimension ref="A1:BP64"/>
+  <dimension ref="A1:BM64"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="64" width="2.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="76.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="67" max="67" width="83.5703125" bestFit="1" customWidth="1"/>
-    <col min="68" max="68" width="172.28515625" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="76.42578125" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1652,23 +1943,12 @@
       <c r="BL1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM1">
-        <v>1</v>
-      </c>
-      <c r="BN1" s="1" t="str">
+      <c r="BM1" s="1" t="str">
         <f>_xlfn.TEXTJOIN("",TRUE,A1:BL1)</f>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO1" t="str">
-        <f>"m$("&amp;BM1&amp;")="&amp;""""&amp;BN1&amp;""""</f>
-        <v>m$(1)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP1" t="str">
-        <f>"{"&amp;""""&amp;BN1&amp;""""&amp;"},"</f>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="2" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -1769,7 +2049,7 @@
         <v>0</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="AI2" s="2">
         <v>0</v>
@@ -1861,23 +2141,12 @@
       <c r="BL2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM2">
-        <v>2</v>
-      </c>
-      <c r="BN2" s="1" t="str">
-        <f t="shared" ref="BN2:BN64" si="0">_xlfn.TEXTJOIN("",TRUE,A2:BL2)</f>
-        <v>XXXXXXXXXXXXXXXXXXXXXXXXXXX0000D0H00A00A00XXXXXXXXXXXXXXXXXXXXXX</v>
-      </c>
-      <c r="BO2" t="str">
-        <f t="shared" ref="BO2:BO64" si="1">"m$("&amp;BM2&amp;")="&amp;""""&amp;BN2&amp;""""</f>
-        <v>m$(2)="XXXXXXXXXXXXXXXXXXXXXXXXXXX0000D0H00A00A00XXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP2" t="str">
-        <f t="shared" ref="BP2:BP64" si="2">"{"&amp;""""&amp;BN2&amp;""""&amp;"},"</f>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXX0000D0H00A00A00XXXXXXXXXXXXXXXXXXXXXX"},</v>
+      <c r="BM2" s="1" t="str">
+        <f t="shared" ref="BM2:BM64" si="0">_xlfn.TEXTJOIN("",TRUE,A2:BL2)</f>
+        <v>XXXXXXXXXXXXXXXXXXXXXXXXXXX0000D0C00A00A00XXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
     </row>
-    <row r="3" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -1966,7 +2235,7 @@
         <v>0</v>
       </c>
       <c r="AD3" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AE3" s="2" t="s">
         <v>0</v>
@@ -2070,23 +2339,12 @@
       <c r="BL3" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM3">
-        <v>3</v>
-      </c>
-      <c r="BN3" s="1" t="str">
+      <c r="BM3" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXAXBXXXSXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO3" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(3)="XXXXXXXXXXXXXXXXXXXXXXXXXXXAXBXXXSXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP3" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXAXBXXXSXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="4" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>0</v>
       </c>
@@ -2279,23 +2537,12 @@
       <c r="BL4" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM4">
-        <v>4</v>
-      </c>
-      <c r="BN4" s="1" t="str">
+      <c r="BM4" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXX00000XXX0XXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO4" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(4)="XXXXXXXXXXXXXXXXXXXXXXXXX00000XXX0XXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP4" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXX00000XXX0XXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="5" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>0</v>
       </c>
@@ -2375,13 +2622,13 @@
         <v>0</v>
       </c>
       <c r="AA5" s="2" t="s">
-        <v>6</v>
+        <v>58</v>
       </c>
       <c r="AB5" s="2">
         <v>0</v>
       </c>
       <c r="AC5" s="2" t="s">
-        <v>6</v>
+        <v>59</v>
       </c>
       <c r="AD5" s="2">
         <v>0</v>
@@ -2488,23 +2735,12 @@
       <c r="BL5" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM5">
-        <v>5</v>
-      </c>
-      <c r="BN5" s="1" t="str">
+      <c r="BM5" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>XXXXXXXXXXXXXXXXXXXXXXXXX0H0H0XXXSXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
-      </c>
-      <c r="BO5" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(5)="XXXXXXXXXXXXXXXXXXXXXXXXX0H0H0XXXSXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP5" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXX0H0H0XXXSXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
+        <v>XXXXXXXXXXXXXXXXXXXXXXXXX0E0F0XXXSXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
     </row>
-    <row r="6" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>0</v>
       </c>
@@ -2697,23 +2933,12 @@
       <c r="BL6" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM6">
-        <v>6</v>
-      </c>
-      <c r="BN6" s="1" t="str">
+      <c r="BM6" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXX00000D00000D0A00XXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO6" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(6)="XXXXXXXXXXXXXXXXXXX00000D00000D0A00XXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP6" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXX00000D00000D0A00XXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="7" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>0</v>
       </c>
@@ -2795,8 +3020,8 @@
       <c r="AA7" s="2">
         <v>0</v>
       </c>
-      <c r="AB7" s="2">
-        <v>0</v>
+      <c r="AB7" s="2" t="s">
+        <v>60</v>
       </c>
       <c r="AC7" s="2">
         <v>0</v>
@@ -2906,23 +3131,12 @@
       <c r="BL7" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM7">
-        <v>7</v>
-      </c>
-      <c r="BN7" s="1" t="str">
+      <c r="BM7" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>XXXXXXXXXXXXXXXXXXXXXX0XX00000XXXX0XXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
-      </c>
-      <c r="BO7" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(7)="XXXXXXXXXXXXXXXXXXXXXX0XX00000XXXX0XXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP7" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXX0XX00000XXXX0XXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
+        <v>XXXXXXXXXXXXXXXXXXXXXX0XX00G00XXXX0XXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
     </row>
-    <row r="8" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>0</v>
       </c>
@@ -3115,23 +3329,12 @@
       <c r="BL8" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM8">
-        <v>8</v>
-      </c>
-      <c r="BN8" s="1" t="str">
+      <c r="BM8" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXX0XXXX0XXXXXXAXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO8" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(8)="XXXXXXXXXXXXXXXXXXXXXX0XXXX0XXXXXXAXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP8" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXX0XXXX0XXXXXXAXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="9" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>0</v>
       </c>
@@ -3324,23 +3527,12 @@
       <c r="BL9" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM9">
-        <v>9</v>
-      </c>
-      <c r="BN9" s="1" t="str">
+      <c r="BM9" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXX0XXXXDXXXXXX0XXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO9" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(9)="XXXXXXXXXXXXXXXXXXXXXX0XXXXDXXXXXX0XXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP9" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXX0XXXXDXXXXXX0XXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="10" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>0</v>
       </c>
@@ -3533,23 +3725,12 @@
       <c r="BL10" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM10">
-        <v>10</v>
-      </c>
-      <c r="BN10" s="1" t="str">
+      <c r="BM10" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXAXXXX0XXXXXX0XXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO10" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(10)="XXXXXXXXXXXXXXXXXXXXXXAXXXX0XXXXXX0XXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP10" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXAXXXX0XXXXXX0XXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="11" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>0</v>
       </c>
@@ -3742,23 +3923,12 @@
       <c r="BL11" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM11">
-        <v>11</v>
-      </c>
-      <c r="BN11" s="1" t="str">
+      <c r="BM11" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXX000X000XXXXXAXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO11" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(11)="XXXXXXXXXXXXXXXXXXXXXX000X000XXXXXAXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP11" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXX000X000XXXXXAXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="12" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>0</v>
       </c>
@@ -3951,23 +4121,12 @@
       <c r="BL12" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM12">
-        <v>12</v>
-      </c>
-      <c r="BN12" s="1" t="str">
+      <c r="BM12" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXX000W0P0XXXXX0XXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO12" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(12)="XXXXXXXXXXXXXXXXXXXXXX000W0P0XXXXX0XXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP12" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXX000W0P0XXXXX0XXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="13" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>0</v>
       </c>
@@ -4160,23 +4319,12 @@
       <c r="BL13" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM13">
-        <v>13</v>
-      </c>
-      <c r="BN13" s="1" t="str">
+      <c r="BM13" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXX000X000XXXXX0XXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO13" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(13)="XXXXXXXXXXXXXXXXXXXXXX000X000XXXXX0XXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP13" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXX000X000XXXXX0XXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="14" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>0</v>
       </c>
@@ -4369,23 +4517,12 @@
       <c r="BL14" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM14">
-        <v>14</v>
-      </c>
-      <c r="BN14" s="1" t="str">
+      <c r="BM14" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO14" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(14)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP14" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="15" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>0</v>
       </c>
@@ -4578,23 +4715,12 @@
       <c r="BL15" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM15">
-        <v>15</v>
-      </c>
-      <c r="BN15" s="1" t="str">
+      <c r="BM15" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO15" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(15)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP15" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="16" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>0</v>
       </c>
@@ -4787,23 +4913,12 @@
       <c r="BL16" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM16">
-        <v>16</v>
-      </c>
-      <c r="BN16" s="1" t="str">
+      <c r="BM16" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO16" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(16)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP16" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="17" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>0</v>
       </c>
@@ -4996,23 +5111,12 @@
       <c r="BL17" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM17">
-        <v>17</v>
-      </c>
-      <c r="BN17" s="1" t="str">
+      <c r="BM17" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO17" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(17)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP17" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="18" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>0</v>
       </c>
@@ -5205,23 +5309,12 @@
       <c r="BL18" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM18">
-        <v>18</v>
-      </c>
-      <c r="BN18" s="1" t="str">
+      <c r="BM18" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO18" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(18)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP18" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="19" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>0</v>
       </c>
@@ -5414,23 +5507,12 @@
       <c r="BL19" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM19">
-        <v>19</v>
-      </c>
-      <c r="BN19" s="1" t="str">
+      <c r="BM19" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO19" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(19)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP19" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="20" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>0</v>
       </c>
@@ -5623,23 +5705,12 @@
       <c r="BL20" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM20">
-        <v>20</v>
-      </c>
-      <c r="BN20" s="1" t="str">
+      <c r="BM20" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO20" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(20)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP20" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="21" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>0</v>
       </c>
@@ -5832,23 +5903,12 @@
       <c r="BL21" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM21">
-        <v>21</v>
-      </c>
-      <c r="BN21" s="1" t="str">
+      <c r="BM21" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO21" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(21)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP21" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="22" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>0</v>
       </c>
@@ -6041,23 +6101,12 @@
       <c r="BL22" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM22">
-        <v>22</v>
-      </c>
-      <c r="BN22" s="1" t="str">
+      <c r="BM22" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO22" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(22)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP22" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="23" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>0</v>
       </c>
@@ -6250,23 +6299,12 @@
       <c r="BL23" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM23">
-        <v>23</v>
-      </c>
-      <c r="BN23" s="1" t="str">
+      <c r="BM23" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO23" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(23)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP23" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="24" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>0</v>
       </c>
@@ -6459,23 +6497,12 @@
       <c r="BL24" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM24">
-        <v>24</v>
-      </c>
-      <c r="BN24" s="1" t="str">
+      <c r="BM24" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO24" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(24)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP24" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="25" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>0</v>
       </c>
@@ -6668,23 +6695,12 @@
       <c r="BL25" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM25">
-        <v>25</v>
-      </c>
-      <c r="BN25" s="1" t="str">
+      <c r="BM25" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO25" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(25)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP25" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="26" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>0</v>
       </c>
@@ -6877,23 +6893,12 @@
       <c r="BL26" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM26">
-        <v>26</v>
-      </c>
-      <c r="BN26" s="1" t="str">
+      <c r="BM26" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO26" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(26)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP26" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="27" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>0</v>
       </c>
@@ -7086,23 +7091,12 @@
       <c r="BL27" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM27">
-        <v>27</v>
-      </c>
-      <c r="BN27" s="1" t="str">
+      <c r="BM27" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO27" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(27)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP27" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="28" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>0</v>
       </c>
@@ -7295,23 +7289,12 @@
       <c r="BL28" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM28">
-        <v>28</v>
-      </c>
-      <c r="BN28" s="1" t="str">
+      <c r="BM28" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO28" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(28)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP28" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="29" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>0</v>
       </c>
@@ -7504,23 +7487,12 @@
       <c r="BL29" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM29">
-        <v>29</v>
-      </c>
-      <c r="BN29" s="1" t="str">
+      <c r="BM29" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO29" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(29)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP29" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="30" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>0</v>
       </c>
@@ -7713,23 +7685,12 @@
       <c r="BL30" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM30">
-        <v>30</v>
-      </c>
-      <c r="BN30" s="1" t="str">
+      <c r="BM30" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO30" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(30)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP30" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="31" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>0</v>
       </c>
@@ -7922,23 +7883,12 @@
       <c r="BL31" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM31">
-        <v>31</v>
-      </c>
-      <c r="BN31" s="1" t="str">
+      <c r="BM31" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO31" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(31)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP31" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="32" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>0</v>
       </c>
@@ -8131,23 +8081,12 @@
       <c r="BL32" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM32">
-        <v>32</v>
-      </c>
-      <c r="BN32" s="1" t="str">
+      <c r="BM32" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO32" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(32)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP32" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="33" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>0</v>
       </c>
@@ -8340,23 +8279,12 @@
       <c r="BL33" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM33">
-        <v>33</v>
-      </c>
-      <c r="BN33" s="1" t="str">
+      <c r="BM33" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO33" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(33)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP33" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="34" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>0</v>
       </c>
@@ -8549,23 +8477,12 @@
       <c r="BL34" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM34">
-        <v>34</v>
-      </c>
-      <c r="BN34" s="1" t="str">
+      <c r="BM34" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO34" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(34)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP34" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="35" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>0</v>
       </c>
@@ -8758,23 +8675,12 @@
       <c r="BL35" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM35">
-        <v>35</v>
-      </c>
-      <c r="BN35" s="1" t="str">
+      <c r="BM35" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO35" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(35)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP35" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="36" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>0</v>
       </c>
@@ -8967,23 +8873,12 @@
       <c r="BL36" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM36">
-        <v>36</v>
-      </c>
-      <c r="BN36" s="1" t="str">
+      <c r="BM36" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO36" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(36)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP36" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="37" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>0</v>
       </c>
@@ -9176,23 +9071,12 @@
       <c r="BL37" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM37">
-        <v>37</v>
-      </c>
-      <c r="BN37" s="1" t="str">
+      <c r="BM37" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO37" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(37)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP37" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="38" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>0</v>
       </c>
@@ -9385,23 +9269,12 @@
       <c r="BL38" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM38">
-        <v>38</v>
-      </c>
-      <c r="BN38" s="1" t="str">
+      <c r="BM38" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO38" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(38)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP38" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="39" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>0</v>
       </c>
@@ -9594,23 +9467,12 @@
       <c r="BL39" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM39">
-        <v>39</v>
-      </c>
-      <c r="BN39" s="1" t="str">
+      <c r="BM39" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO39" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(39)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP39" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="40" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>0</v>
       </c>
@@ -9803,23 +9665,12 @@
       <c r="BL40" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM40">
-        <v>40</v>
-      </c>
-      <c r="BN40" s="1" t="str">
+      <c r="BM40" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO40" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(40)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP40" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="41" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>0</v>
       </c>
@@ -10012,23 +9863,12 @@
       <c r="BL41" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM41">
-        <v>41</v>
-      </c>
-      <c r="BN41" s="1" t="str">
+      <c r="BM41" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO41" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(41)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP41" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="42" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>0</v>
       </c>
@@ -10221,23 +10061,12 @@
       <c r="BL42" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM42">
-        <v>42</v>
-      </c>
-      <c r="BN42" s="1" t="str">
+      <c r="BM42" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO42" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(42)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP42" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="43" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>0</v>
       </c>
@@ -10430,23 +10259,12 @@
       <c r="BL43" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM43">
-        <v>43</v>
-      </c>
-      <c r="BN43" s="1" t="str">
+      <c r="BM43" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO43" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(43)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP43" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="44" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>0</v>
       </c>
@@ -10639,23 +10457,12 @@
       <c r="BL44" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM44">
-        <v>44</v>
-      </c>
-      <c r="BN44" s="1" t="str">
+      <c r="BM44" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO44" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(44)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP44" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="45" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>0</v>
       </c>
@@ -10848,23 +10655,12 @@
       <c r="BL45" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM45">
-        <v>45</v>
-      </c>
-      <c r="BN45" s="1" t="str">
+      <c r="BM45" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO45" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(45)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP45" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="46" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>0</v>
       </c>
@@ -11057,23 +10853,12 @@
       <c r="BL46" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM46">
-        <v>46</v>
-      </c>
-      <c r="BN46" s="1" t="str">
+      <c r="BM46" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO46" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(46)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP46" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="47" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>0</v>
       </c>
@@ -11266,23 +11051,12 @@
       <c r="BL47" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM47">
-        <v>47</v>
-      </c>
-      <c r="BN47" s="1" t="str">
+      <c r="BM47" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO47" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(47)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP47" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="48" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>0</v>
       </c>
@@ -11475,23 +11249,12 @@
       <c r="BL48" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM48">
-        <v>48</v>
-      </c>
-      <c r="BN48" s="1" t="str">
+      <c r="BM48" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO48" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(48)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP48" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="49" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>0</v>
       </c>
@@ -11684,23 +11447,12 @@
       <c r="BL49" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM49">
-        <v>49</v>
-      </c>
-      <c r="BN49" s="1" t="str">
+      <c r="BM49" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO49" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(49)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP49" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="50" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>0</v>
       </c>
@@ -11893,23 +11645,12 @@
       <c r="BL50" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM50">
-        <v>50</v>
-      </c>
-      <c r="BN50" s="1" t="str">
+      <c r="BM50" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO50" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(50)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP50" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="51" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>0</v>
       </c>
@@ -12102,23 +11843,12 @@
       <c r="BL51" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM51">
-        <v>51</v>
-      </c>
-      <c r="BN51" s="1" t="str">
+      <c r="BM51" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO51" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(51)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP51" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="52" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>0</v>
       </c>
@@ -12311,23 +12041,12 @@
       <c r="BL52" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM52">
-        <v>52</v>
-      </c>
-      <c r="BN52" s="1" t="str">
+      <c r="BM52" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO52" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(52)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP52" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="53" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>0</v>
       </c>
@@ -12520,23 +12239,12 @@
       <c r="BL53" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM53">
-        <v>53</v>
-      </c>
-      <c r="BN53" s="1" t="str">
+      <c r="BM53" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO53" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(53)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP53" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="54" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>0</v>
       </c>
@@ -12729,23 +12437,12 @@
       <c r="BL54" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM54">
-        <v>54</v>
-      </c>
-      <c r="BN54" s="1" t="str">
+      <c r="BM54" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO54" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(54)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP54" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="55" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>0</v>
       </c>
@@ -12938,23 +12635,12 @@
       <c r="BL55" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM55">
-        <v>55</v>
-      </c>
-      <c r="BN55" s="1" t="str">
+      <c r="BM55" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO55" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(55)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP55" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="56" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>0</v>
       </c>
@@ -13147,23 +12833,12 @@
       <c r="BL56" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM56">
-        <v>56</v>
-      </c>
-      <c r="BN56" s="1" t="str">
+      <c r="BM56" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO56" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(56)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP56" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="57" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>0</v>
       </c>
@@ -13356,23 +13031,12 @@
       <c r="BL57" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM57">
-        <v>57</v>
-      </c>
-      <c r="BN57" s="1" t="str">
+      <c r="BM57" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO57" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(57)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP57" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="58" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>0</v>
       </c>
@@ -13565,23 +13229,12 @@
       <c r="BL58" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM58">
-        <v>58</v>
-      </c>
-      <c r="BN58" s="1" t="str">
+      <c r="BM58" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO58" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(58)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP58" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="59" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>0</v>
       </c>
@@ -13774,23 +13427,12 @@
       <c r="BL59" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM59">
-        <v>59</v>
-      </c>
-      <c r="BN59" s="1" t="str">
+      <c r="BM59" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO59" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(59)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP59" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="60" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>0</v>
       </c>
@@ -13983,23 +13625,12 @@
       <c r="BL60" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM60">
-        <v>60</v>
-      </c>
-      <c r="BN60" s="1" t="str">
+      <c r="BM60" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO60" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(60)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP60" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="61" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>0</v>
       </c>
@@ -14192,23 +13823,12 @@
       <c r="BL61" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM61">
-        <v>61</v>
-      </c>
-      <c r="BN61" s="1" t="str">
+      <c r="BM61" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO61" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(61)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP61" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="62" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>0</v>
       </c>
@@ -14401,23 +14021,12 @@
       <c r="BL62" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM62">
-        <v>62</v>
-      </c>
-      <c r="BN62" s="1" t="str">
+      <c r="BM62" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO62" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(62)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP62" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="63" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>0</v>
       </c>
@@ -14610,23 +14219,12 @@
       <c r="BL63" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM63">
-        <v>63</v>
-      </c>
-      <c r="BN63" s="1" t="str">
+      <c r="BM63" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO63" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(63)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP63" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="64" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>0</v>
       </c>
@@ -14819,141 +14417,161 @@
       <c r="BL64" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM64">
-        <v>64</v>
-      </c>
-      <c r="BN64" s="1" t="str">
+      <c r="BM64" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
-      </c>
-      <c r="BO64" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(64)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP64" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:BL64">
-    <cfRule type="containsText" dxfId="6" priority="7" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="9" priority="11" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH("X",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:BL1048576">
-    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
+      <formula>"G"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
+      <formula>"F"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="3" operator="equal">
+      <formula>"E"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="5" priority="5" operator="equal">
       <formula>"B"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
-      <formula>"H"</formula>
+    <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
+      <formula>"C"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="7" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="8" operator="equal">
       <formula>"D"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="9" operator="equal">
       <formula>"P"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="10" operator="equal">
       <formula>"W"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE5E0410-6B34-4610-813C-474405B474F7}">
-  <dimension ref="A2:D12"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="9.140625" style="5"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B1" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B2">
+        <v>15</v>
+      </c>
+      <c r="B2" s="5">
         <f>256*160*2/8</f>
         <v>10240</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3">
-        <f>64*64</f>
-        <v>4096</v>
+        <v>16</v>
+      </c>
+      <c r="B3" s="5">
+        <v>8192</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B4">
+        <v>53</v>
+      </c>
+      <c r="B4" s="5">
         <f>2*1024</f>
         <v>2048</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B5">
+        <v>54</v>
+      </c>
+      <c r="B5" s="5">
         <f>8*1024</f>
         <v>8192</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>56</v>
-      </c>
-      <c r="B6">
+        <v>55</v>
+      </c>
+      <c r="B6" s="5">
         <f>HEX2DEC("2000")</f>
         <v>8192</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>57</v>
-      </c>
-      <c r="B7">
+        <v>56</v>
+      </c>
+      <c r="B7" s="5">
         <v>4096</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>58</v>
-      </c>
-      <c r="B8">
+        <v>57</v>
+      </c>
+      <c r="B8" s="5">
         <v>1024</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10">
-        <f>SUM(B2:B8)</f>
-        <v>37888</v>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" s="5">
+        <f>1024*31</f>
+        <v>31744</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12">
-        <f>65536-B10</f>
-        <v>27648</v>
-      </c>
-      <c r="D12" s="4">
+        <v>17</v>
+      </c>
+      <c r="B12" s="5">
+        <f>SUM(B2:B8)</f>
+        <v>41984</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="5">
+        <f>65536-B12</f>
+        <v>23552</v>
+      </c>
+      <c r="C14" s="5">
         <f>B12/65536</f>
-        <v>0.421875</v>
+        <v>0.640625</v>
+      </c>
+      <c r="D14" s="4">
+        <f>B14/65536</f>
+        <v>0.359375</v>
       </c>
     </row>
   </sheetData>
@@ -14971,30 +14589,30 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J1" t="s">
         <v>44</v>
-      </c>
-      <c r="D1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F1" t="s">
-        <v>39</v>
-      </c>
-      <c r="G1" t="s">
-        <v>44</v>
-      </c>
-      <c r="H1" t="s">
-        <v>43</v>
-      </c>
-      <c r="J1" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B2">
         <v>16</v>
@@ -15021,7 +14639,7 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B3">
         <v>640</v>
@@ -15051,7 +14669,7 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B4">
         <v>20</v>
@@ -15083,27 +14701,27 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB40D263-C04C-4263-859C-02DFCB83777C}">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.140625" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B2">
         <v>130</v>
@@ -15119,27 +14737,27 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B3">
         <v>140</v>
       </c>
       <c r="C3" s="4">
-        <f t="shared" ref="C3:C9" si="0">(B3/$B$2)-1</f>
+        <f t="shared" ref="C3:C11" si="0">(B3/$B$2)-1</f>
         <v>7.6923076923076872E-2</v>
       </c>
       <c r="E3">
-        <f t="shared" ref="E3:E9" si="1">B3/40</f>
+        <f t="shared" ref="E3:E11" si="1">B3/40</f>
         <v>3.5</v>
       </c>
       <c r="F3">
-        <f t="shared" ref="F3:F9" si="2">E3/3</f>
+        <f t="shared" ref="F3:F11" si="2">E3/3</f>
         <v>1.1666666666666667</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B4">
         <v>360</v>
@@ -15159,7 +14777,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B5">
         <v>360</v>
@@ -15179,7 +14797,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B6">
         <v>630</v>
@@ -15199,7 +14817,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B7">
         <v>410</v>
@@ -15219,7 +14837,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B8">
         <v>530</v>
@@ -15239,7 +14857,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B9">
         <v>570</v>
@@ -15255,6 +14873,46 @@
       <c r="F9">
         <f t="shared" si="2"/>
         <v>4.75</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>99</v>
+      </c>
+      <c r="B10">
+        <v>600</v>
+      </c>
+      <c r="C10" s="4">
+        <f t="shared" si="0"/>
+        <v>3.615384615384615</v>
+      </c>
+      <c r="E10">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="F10">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>100</v>
+      </c>
+      <c r="B11">
+        <v>600</v>
+      </c>
+      <c r="C11" s="4">
+        <f t="shared" si="0"/>
+        <v>3.615384615384615</v>
+      </c>
+      <c r="E11">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="F11">
+        <f t="shared" si="2"/>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/Psion Levels.xlsx
+++ b/Psion Levels.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Zak\Documents\GitProjects\psion3d\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{324A20A8-1F1D-497D-BA11-3D9E1746D0E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82C4A731-B6EF-4052-8A28-D794440D9CF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{72A343FB-71F0-4738-BBFF-B23B40D170FF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{72A343FB-71F0-4738-BBFF-B23B40D170FF}"/>
   </bookViews>
   <sheets>
     <sheet name="Mapbits" sheetId="4" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="9" r:id="rId2"/>
-    <sheet name="Sheet1" sheetId="8" r:id="rId3"/>
+    <sheet name="AI States" sheetId="8" r:id="rId3"/>
     <sheet name="Tiles Type" sheetId="2" r:id="rId4"/>
     <sheet name="Level 1" sheetId="1" r:id="rId5"/>
     <sheet name="Memory Budget" sheetId="3" r:id="rId6"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4204" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4227" uniqueCount="101">
   <si>
     <t>X</t>
   </si>
@@ -64,9 +64,6 @@
   </si>
   <si>
     <t>S</t>
-  </si>
-  <si>
-    <t>H</t>
   </si>
   <si>
     <t>Type</t>
@@ -88,9 +85,6 @@
   </si>
   <si>
     <t>Unlocked Door</t>
-  </si>
-  <si>
-    <t>Health Pack</t>
   </si>
   <si>
     <t>Secret Wall</t>
@@ -145,6 +139,9 @@
   </si>
   <si>
     <t>Sprite</t>
+  </si>
+  <si>
+    <t>Id</t>
   </si>
   <si>
     <t>Bit</t>
@@ -228,19 +225,10 @@
     <t>E</t>
   </si>
   <si>
-    <t>Fodder enemy</t>
-  </si>
-  <si>
-    <t>Mid Enemy</t>
-  </si>
-  <si>
     <t>F</t>
   </si>
   <si>
     <t>G</t>
-  </si>
-  <si>
-    <t>Heavy Enetmy</t>
   </si>
   <si>
     <t>Civilian</t>
@@ -323,6 +311,45 @@
   <si>
     <t>Block contains an enemy.</t>
   </si>
+  <si>
+    <t>Game Seg</t>
+  </si>
+  <si>
+    <t>Other Segs</t>
+  </si>
+  <si>
+    <t>Mercenary enemy</t>
+  </si>
+  <si>
+    <t>Soldier Enemy</t>
+  </si>
+  <si>
+    <t>Heavy Enemy</t>
+  </si>
+  <si>
+    <t>Wall types</t>
+  </si>
+  <si>
+    <t>Default wall</t>
+  </si>
+  <si>
+    <t>Dark Wall</t>
+  </si>
+  <si>
+    <t>Bars</t>
+  </si>
+  <si>
+    <t>Enemy Types</t>
+  </si>
+  <si>
+    <t>Soldier</t>
+  </si>
+  <si>
+    <t>Bitmask maps</t>
+  </si>
+  <si>
+    <t>U16 map</t>
+  </si>
 </sst>
 </file>
 
@@ -372,7 +399,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -382,11 +409,107 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFF00"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -778,7 +901,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A21D89A8-E5EC-4EAA-92CE-B056DD4B8657}">
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.5703125" bestFit="1" customWidth="1"/>
@@ -789,134 +912,326 @@
     <col min="6" max="6" width="9.85546875" customWidth="1"/>
     <col min="7" max="7" width="11" customWidth="1"/>
     <col min="8" max="8" width="13" customWidth="1"/>
+    <col min="9" max="9" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B1" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="F1" t="s">
+        <v>93</v>
+      </c>
+      <c r="G1">
+        <v>0</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="I1" t="s">
+        <v>94</v>
+      </c>
+      <c r="K1" t="s">
+        <v>97</v>
+      </c>
+      <c r="L1">
+        <v>0</v>
+      </c>
+      <c r="M1" t="s">
+        <v>61</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C2" t="s">
-        <v>34</v>
+        <v>33</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I2" t="s">
+        <v>95</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2" t="s">
+        <v>79</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s">
         <v>35</v>
       </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="I3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3" t="s">
+        <v>98</v>
+      </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="G4">
+        <v>3</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I4" t="s">
+        <v>11</v>
+      </c>
+      <c r="L4">
+        <v>3</v>
+      </c>
+      <c r="M4" t="s">
+        <v>81</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>34</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I5" t="s">
+        <v>12</v>
+      </c>
+      <c r="L5">
+        <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>31</v>
+        <v>86</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>87</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I6" t="s">
+        <v>13</v>
+      </c>
+      <c r="L6">
+        <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>91</v>
+        <v>36</v>
+      </c>
+      <c r="G7">
+        <v>6</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I7" t="s">
+        <v>96</v>
+      </c>
+      <c r="L7">
+        <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>9</v>
       </c>
+      <c r="B8" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="G8">
+        <v>7</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L8">
+        <v>7</v>
+      </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
+      <c r="B9" s="6"/>
+      <c r="G9">
+        <v>8</v>
+      </c>
+      <c r="L9">
+        <v>8</v>
+      </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>7</v>
       </c>
+      <c r="B10" s="6"/>
+      <c r="C10" s="7"/>
+      <c r="G10">
+        <v>9</v>
+      </c>
+      <c r="L10">
+        <v>9</v>
+      </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>6</v>
       </c>
+      <c r="B11" s="6"/>
+      <c r="C11" s="7"/>
+      <c r="G11">
+        <v>10</v>
+      </c>
+      <c r="L11">
+        <v>10</v>
+      </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>5</v>
       </c>
+      <c r="B12" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="7"/>
+      <c r="G12">
+        <v>11</v>
+      </c>
+      <c r="L12">
+        <v>11</v>
+      </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>4</v>
       </c>
+      <c r="B13" s="6"/>
+      <c r="C13" s="7"/>
+      <c r="G13">
+        <v>12</v>
+      </c>
+      <c r="L13">
+        <v>12</v>
+      </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>3</v>
       </c>
+      <c r="B14" s="6"/>
+      <c r="C14" s="7"/>
+      <c r="G14">
+        <v>13</v>
+      </c>
+      <c r="L14">
+        <v>13</v>
+      </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2</v>
       </c>
+      <c r="B15" s="6"/>
+      <c r="C15" s="7"/>
+      <c r="G15">
+        <v>14</v>
+      </c>
+      <c r="L15">
+        <v>14</v>
+      </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>1</v>
       </c>
+      <c r="B16" s="6"/>
+      <c r="C16" s="7"/>
+      <c r="G16">
+        <v>15</v>
+      </c>
+      <c r="L16">
+        <v>15</v>
+      </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>0</v>
       </c>
+      <c r="B17" s="6"/>
+      <c r="C17" s="7"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B8:B11"/>
+    <mergeCell ref="B12:B17"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -930,7 +1245,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -938,7 +1253,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -946,7 +1261,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -954,7 +1269,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -962,7 +1277,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -984,10 +1299,10 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -995,13 +1310,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2" t="s">
         <v>68</v>
-      </c>
-      <c r="E2" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -1009,16 +1324,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E3" t="s">
         <v>69</v>
       </c>
-      <c r="E3" t="s">
-        <v>73</v>
-      </c>
       <c r="F3" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1026,16 +1341,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E4" t="s">
         <v>70</v>
       </c>
-      <c r="E4" t="s">
-        <v>74</v>
-      </c>
       <c r="F4" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -1043,13 +1358,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D5" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="E5" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -1057,7 +1372,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -1065,7 +1380,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -1073,7 +1388,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -1081,7 +1396,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -1091,34 +1406,34 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3F90467-4CD9-40FD-80C5-3B27CEDF7551}">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
         <v>7</v>
       </c>
-      <c r="B1" t="s">
-        <v>8</v>
-      </c>
       <c r="C1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -1126,22 +1441,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -1149,22 +1464,22 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1172,22 +1487,22 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -1195,22 +1510,22 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -1218,22 +1533,22 @@
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -1241,68 +1556,68 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F8" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G8" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D9" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E9" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F9" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G9" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -1313,42 +1628,42 @@
         <v>22</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D10" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E10" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F10" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G10" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" t="s">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B12" t="s">
+        <v>90</v>
+      </c>
+      <c r="C12" t="s">
         <v>24</v>
       </c>
-      <c r="C11" t="s">
-        <v>27</v>
-      </c>
-      <c r="D11" t="s">
-        <v>27</v>
-      </c>
-      <c r="E11" t="s">
-        <v>26</v>
-      </c>
-      <c r="F11" t="s">
-        <v>26</v>
-      </c>
-      <c r="G11" t="s">
-        <v>26</v>
+      <c r="D12" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" t="s">
+        <v>25</v>
+      </c>
+      <c r="G12" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -1356,110 +1671,86 @@
         <v>59</v>
       </c>
       <c r="B13" t="s">
-        <v>60</v>
+        <v>91</v>
       </c>
       <c r="C13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B14" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="C14" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D14" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E14" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F14" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G14" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="B15" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C15" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D15" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E15" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F15" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G15" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B16" t="s">
-        <v>65</v>
-      </c>
-      <c r="C16" t="s">
-        <v>26</v>
-      </c>
-      <c r="D16" t="s">
-        <v>26</v>
-      </c>
-      <c r="E16" t="s">
-        <v>27</v>
-      </c>
-      <c r="F16" t="s">
-        <v>27</v>
-      </c>
-      <c r="G16" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{750D9AD9-7C84-4603-A2EE-1597D412FCF4}">
-  <dimension ref="A1:BP64"/>
+  <dimension ref="A1:BM64"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="64" width="2.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="76.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="67" max="67" width="83.5703125" bestFit="1" customWidth="1"/>
-    <col min="68" max="68" width="172.28515625" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="76.42578125" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1652,23 +1943,12 @@
       <c r="BL1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM1">
-        <v>1</v>
-      </c>
-      <c r="BN1" s="1" t="str">
+      <c r="BM1" s="1" t="str">
         <f>_xlfn.TEXTJOIN("",TRUE,A1:BL1)</f>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO1" t="str">
-        <f>"m$("&amp;BM1&amp;")="&amp;""""&amp;BN1&amp;""""</f>
-        <v>m$(1)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP1" t="str">
-        <f>"{"&amp;""""&amp;BN1&amp;""""&amp;"},"</f>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="2" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -1769,7 +2049,7 @@
         <v>0</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="AI2" s="2">
         <v>0</v>
@@ -1861,23 +2141,12 @@
       <c r="BL2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM2">
-        <v>2</v>
-      </c>
-      <c r="BN2" s="1" t="str">
-        <f t="shared" ref="BN2:BN64" si="0">_xlfn.TEXTJOIN("",TRUE,A2:BL2)</f>
-        <v>XXXXXXXXXXXXXXXXXXXXXXXXXXX0000D0H00A00A00XXXXXXXXXXXXXXXXXXXXXX</v>
-      </c>
-      <c r="BO2" t="str">
-        <f t="shared" ref="BO2:BO64" si="1">"m$("&amp;BM2&amp;")="&amp;""""&amp;BN2&amp;""""</f>
-        <v>m$(2)="XXXXXXXXXXXXXXXXXXXXXXXXXXX0000D0H00A00A00XXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP2" t="str">
-        <f t="shared" ref="BP2:BP64" si="2">"{"&amp;""""&amp;BN2&amp;""""&amp;"},"</f>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXX0000D0H00A00A00XXXXXXXXXXXXXXXXXXXXXX"},</v>
+      <c r="BM2" s="1" t="str">
+        <f t="shared" ref="BM2:BM64" si="0">_xlfn.TEXTJOIN("",TRUE,A2:BL2)</f>
+        <v>XXXXXXXXXXXXXXXXXXXXXXXXXXX0000D0C00A00A00XXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
     </row>
-    <row r="3" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -1966,7 +2235,7 @@
         <v>0</v>
       </c>
       <c r="AD3" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AE3" s="2" t="s">
         <v>0</v>
@@ -2070,23 +2339,12 @@
       <c r="BL3" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM3">
-        <v>3</v>
-      </c>
-      <c r="BN3" s="1" t="str">
+      <c r="BM3" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXAXBXXXSXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO3" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(3)="XXXXXXXXXXXXXXXXXXXXXXXXXXXAXBXXXSXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP3" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXAXBXXXSXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="4" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>0</v>
       </c>
@@ -2279,23 +2537,12 @@
       <c r="BL4" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM4">
-        <v>4</v>
-      </c>
-      <c r="BN4" s="1" t="str">
+      <c r="BM4" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXX00000XXX0XXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO4" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(4)="XXXXXXXXXXXXXXXXXXXXXXXXX00000XXX0XXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP4" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXX00000XXX0XXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="5" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>0</v>
       </c>
@@ -2375,13 +2622,13 @@
         <v>0</v>
       </c>
       <c r="AA5" s="2" t="s">
-        <v>6</v>
+        <v>58</v>
       </c>
       <c r="AB5" s="2">
         <v>0</v>
       </c>
       <c r="AC5" s="2" t="s">
-        <v>6</v>
+        <v>59</v>
       </c>
       <c r="AD5" s="2">
         <v>0</v>
@@ -2488,23 +2735,12 @@
       <c r="BL5" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM5">
-        <v>5</v>
-      </c>
-      <c r="BN5" s="1" t="str">
+      <c r="BM5" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>XXXXXXXXXXXXXXXXXXXXXXXXX0H0H0XXXSXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
-      </c>
-      <c r="BO5" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(5)="XXXXXXXXXXXXXXXXXXXXXXXXX0H0H0XXXSXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP5" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXX0H0H0XXXSXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
+        <v>XXXXXXXXXXXXXXXXXXXXXXXXX0E0F0XXXSXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
     </row>
-    <row r="6" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>0</v>
       </c>
@@ -2697,23 +2933,12 @@
       <c r="BL6" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM6">
-        <v>6</v>
-      </c>
-      <c r="BN6" s="1" t="str">
+      <c r="BM6" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXX00000D00000D0A00XXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO6" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(6)="XXXXXXXXXXXXXXXXXXX00000D00000D0A00XXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP6" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXX00000D00000D0A00XXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="7" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>0</v>
       </c>
@@ -2795,8 +3020,8 @@
       <c r="AA7" s="2">
         <v>0</v>
       </c>
-      <c r="AB7" s="2">
-        <v>0</v>
+      <c r="AB7" s="2" t="s">
+        <v>60</v>
       </c>
       <c r="AC7" s="2">
         <v>0</v>
@@ -2906,23 +3131,12 @@
       <c r="BL7" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM7">
-        <v>7</v>
-      </c>
-      <c r="BN7" s="1" t="str">
+      <c r="BM7" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>XXXXXXXXXXXXXXXXXXXXXX0XX00000XXXX0XXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
-      </c>
-      <c r="BO7" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(7)="XXXXXXXXXXXXXXXXXXXXXX0XX00000XXXX0XXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP7" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXX0XX00000XXXX0XXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
+        <v>XXXXXXXXXXXXXXXXXXXXXX0XX00G00XXXX0XXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
     </row>
-    <row r="8" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>0</v>
       </c>
@@ -3115,23 +3329,12 @@
       <c r="BL8" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM8">
-        <v>8</v>
-      </c>
-      <c r="BN8" s="1" t="str">
+      <c r="BM8" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXX0XXXX0XXXXXXAXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO8" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(8)="XXXXXXXXXXXXXXXXXXXXXX0XXXX0XXXXXXAXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP8" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXX0XXXX0XXXXXXAXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="9" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>0</v>
       </c>
@@ -3324,23 +3527,12 @@
       <c r="BL9" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM9">
-        <v>9</v>
-      </c>
-      <c r="BN9" s="1" t="str">
+      <c r="BM9" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXX0XXXXDXXXXXX0XXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO9" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(9)="XXXXXXXXXXXXXXXXXXXXXX0XXXXDXXXXXX0XXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP9" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXX0XXXXDXXXXXX0XXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="10" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>0</v>
       </c>
@@ -3533,23 +3725,12 @@
       <c r="BL10" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM10">
-        <v>10</v>
-      </c>
-      <c r="BN10" s="1" t="str">
+      <c r="BM10" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXAXXXX0XXXXXX0XXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO10" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(10)="XXXXXXXXXXXXXXXXXXXXXXAXXXX0XXXXXX0XXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP10" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXAXXXX0XXXXXX0XXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="11" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>0</v>
       </c>
@@ -3742,23 +3923,12 @@
       <c r="BL11" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM11">
-        <v>11</v>
-      </c>
-      <c r="BN11" s="1" t="str">
+      <c r="BM11" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXX000X000XXXXXAXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO11" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(11)="XXXXXXXXXXXXXXXXXXXXXX000X000XXXXXAXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP11" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXX000X000XXXXXAXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="12" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>0</v>
       </c>
@@ -3951,23 +4121,12 @@
       <c r="BL12" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM12">
-        <v>12</v>
-      </c>
-      <c r="BN12" s="1" t="str">
+      <c r="BM12" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXX000W0P0XXXXX0XXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO12" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(12)="XXXXXXXXXXXXXXXXXXXXXX000W0P0XXXXX0XXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP12" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXX000W0P0XXXXX0XXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="13" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>0</v>
       </c>
@@ -4160,23 +4319,12 @@
       <c r="BL13" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM13">
-        <v>13</v>
-      </c>
-      <c r="BN13" s="1" t="str">
+      <c r="BM13" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXX000X000XXXXX0XXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO13" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(13)="XXXXXXXXXXXXXXXXXXXXXX000X000XXXXX0XXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP13" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXX000X000XXXXX0XXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="14" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>0</v>
       </c>
@@ -4369,23 +4517,12 @@
       <c r="BL14" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM14">
-        <v>14</v>
-      </c>
-      <c r="BN14" s="1" t="str">
+      <c r="BM14" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO14" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(14)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP14" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="15" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>0</v>
       </c>
@@ -4578,23 +4715,12 @@
       <c r="BL15" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM15">
-        <v>15</v>
-      </c>
-      <c r="BN15" s="1" t="str">
+      <c r="BM15" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO15" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(15)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP15" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="16" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>0</v>
       </c>
@@ -4787,23 +4913,12 @@
       <c r="BL16" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM16">
-        <v>16</v>
-      </c>
-      <c r="BN16" s="1" t="str">
+      <c r="BM16" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO16" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(16)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP16" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="17" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>0</v>
       </c>
@@ -4996,23 +5111,12 @@
       <c r="BL17" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM17">
-        <v>17</v>
-      </c>
-      <c r="BN17" s="1" t="str">
+      <c r="BM17" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO17" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(17)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP17" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="18" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>0</v>
       </c>
@@ -5205,23 +5309,12 @@
       <c r="BL18" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM18">
-        <v>18</v>
-      </c>
-      <c r="BN18" s="1" t="str">
+      <c r="BM18" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO18" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(18)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP18" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="19" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>0</v>
       </c>
@@ -5414,23 +5507,12 @@
       <c r="BL19" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM19">
-        <v>19</v>
-      </c>
-      <c r="BN19" s="1" t="str">
+      <c r="BM19" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO19" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(19)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP19" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="20" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>0</v>
       </c>
@@ -5623,23 +5705,12 @@
       <c r="BL20" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM20">
-        <v>20</v>
-      </c>
-      <c r="BN20" s="1" t="str">
+      <c r="BM20" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO20" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(20)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP20" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="21" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>0</v>
       </c>
@@ -5832,23 +5903,12 @@
       <c r="BL21" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM21">
-        <v>21</v>
-      </c>
-      <c r="BN21" s="1" t="str">
+      <c r="BM21" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO21" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(21)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP21" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="22" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>0</v>
       </c>
@@ -6041,23 +6101,12 @@
       <c r="BL22" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM22">
-        <v>22</v>
-      </c>
-      <c r="BN22" s="1" t="str">
+      <c r="BM22" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO22" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(22)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP22" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="23" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>0</v>
       </c>
@@ -6250,23 +6299,12 @@
       <c r="BL23" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM23">
-        <v>23</v>
-      </c>
-      <c r="BN23" s="1" t="str">
+      <c r="BM23" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO23" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(23)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP23" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="24" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>0</v>
       </c>
@@ -6459,23 +6497,12 @@
       <c r="BL24" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM24">
-        <v>24</v>
-      </c>
-      <c r="BN24" s="1" t="str">
+      <c r="BM24" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO24" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(24)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP24" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="25" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>0</v>
       </c>
@@ -6668,23 +6695,12 @@
       <c r="BL25" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM25">
-        <v>25</v>
-      </c>
-      <c r="BN25" s="1" t="str">
+      <c r="BM25" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO25" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(25)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP25" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="26" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>0</v>
       </c>
@@ -6877,23 +6893,12 @@
       <c r="BL26" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM26">
-        <v>26</v>
-      </c>
-      <c r="BN26" s="1" t="str">
+      <c r="BM26" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO26" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(26)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP26" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="27" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>0</v>
       </c>
@@ -7086,23 +7091,12 @@
       <c r="BL27" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM27">
-        <v>27</v>
-      </c>
-      <c r="BN27" s="1" t="str">
+      <c r="BM27" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO27" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(27)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP27" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="28" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>0</v>
       </c>
@@ -7295,23 +7289,12 @@
       <c r="BL28" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM28">
-        <v>28</v>
-      </c>
-      <c r="BN28" s="1" t="str">
+      <c r="BM28" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO28" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(28)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP28" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="29" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>0</v>
       </c>
@@ -7504,23 +7487,12 @@
       <c r="BL29" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM29">
-        <v>29</v>
-      </c>
-      <c r="BN29" s="1" t="str">
+      <c r="BM29" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO29" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(29)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP29" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="30" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>0</v>
       </c>
@@ -7713,23 +7685,12 @@
       <c r="BL30" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM30">
-        <v>30</v>
-      </c>
-      <c r="BN30" s="1" t="str">
+      <c r="BM30" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO30" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(30)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP30" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="31" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>0</v>
       </c>
@@ -7922,23 +7883,12 @@
       <c r="BL31" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM31">
-        <v>31</v>
-      </c>
-      <c r="BN31" s="1" t="str">
+      <c r="BM31" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO31" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(31)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP31" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="32" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>0</v>
       </c>
@@ -8131,23 +8081,12 @@
       <c r="BL32" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM32">
-        <v>32</v>
-      </c>
-      <c r="BN32" s="1" t="str">
+      <c r="BM32" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO32" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(32)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP32" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="33" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>0</v>
       </c>
@@ -8340,23 +8279,12 @@
       <c r="BL33" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM33">
-        <v>33</v>
-      </c>
-      <c r="BN33" s="1" t="str">
+      <c r="BM33" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO33" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(33)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP33" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="34" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>0</v>
       </c>
@@ -8549,23 +8477,12 @@
       <c r="BL34" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM34">
-        <v>34</v>
-      </c>
-      <c r="BN34" s="1" t="str">
+      <c r="BM34" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO34" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(34)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP34" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="35" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>0</v>
       </c>
@@ -8758,23 +8675,12 @@
       <c r="BL35" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM35">
-        <v>35</v>
-      </c>
-      <c r="BN35" s="1" t="str">
+      <c r="BM35" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO35" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(35)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP35" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="36" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>0</v>
       </c>
@@ -8967,23 +8873,12 @@
       <c r="BL36" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM36">
-        <v>36</v>
-      </c>
-      <c r="BN36" s="1" t="str">
+      <c r="BM36" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO36" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(36)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP36" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="37" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>0</v>
       </c>
@@ -9176,23 +9071,12 @@
       <c r="BL37" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM37">
-        <v>37</v>
-      </c>
-      <c r="BN37" s="1" t="str">
+      <c r="BM37" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO37" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(37)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP37" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="38" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>0</v>
       </c>
@@ -9385,23 +9269,12 @@
       <c r="BL38" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM38">
-        <v>38</v>
-      </c>
-      <c r="BN38" s="1" t="str">
+      <c r="BM38" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO38" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(38)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP38" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="39" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>0</v>
       </c>
@@ -9594,23 +9467,12 @@
       <c r="BL39" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM39">
-        <v>39</v>
-      </c>
-      <c r="BN39" s="1" t="str">
+      <c r="BM39" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO39" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(39)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP39" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="40" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>0</v>
       </c>
@@ -9803,23 +9665,12 @@
       <c r="BL40" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM40">
-        <v>40</v>
-      </c>
-      <c r="BN40" s="1" t="str">
+      <c r="BM40" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO40" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(40)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP40" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="41" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>0</v>
       </c>
@@ -10012,23 +9863,12 @@
       <c r="BL41" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM41">
-        <v>41</v>
-      </c>
-      <c r="BN41" s="1" t="str">
+      <c r="BM41" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO41" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(41)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP41" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="42" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>0</v>
       </c>
@@ -10221,23 +10061,12 @@
       <c r="BL42" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM42">
-        <v>42</v>
-      </c>
-      <c r="BN42" s="1" t="str">
+      <c r="BM42" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO42" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(42)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP42" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="43" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>0</v>
       </c>
@@ -10430,23 +10259,12 @@
       <c r="BL43" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM43">
-        <v>43</v>
-      </c>
-      <c r="BN43" s="1" t="str">
+      <c r="BM43" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO43" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(43)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP43" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="44" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>0</v>
       </c>
@@ -10639,23 +10457,12 @@
       <c r="BL44" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM44">
-        <v>44</v>
-      </c>
-      <c r="BN44" s="1" t="str">
+      <c r="BM44" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO44" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(44)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP44" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="45" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>0</v>
       </c>
@@ -10848,23 +10655,12 @@
       <c r="BL45" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM45">
-        <v>45</v>
-      </c>
-      <c r="BN45" s="1" t="str">
+      <c r="BM45" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO45" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(45)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP45" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="46" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>0</v>
       </c>
@@ -11057,23 +10853,12 @@
       <c r="BL46" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM46">
-        <v>46</v>
-      </c>
-      <c r="BN46" s="1" t="str">
+      <c r="BM46" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO46" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(46)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP46" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="47" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>0</v>
       </c>
@@ -11266,23 +11051,12 @@
       <c r="BL47" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM47">
-        <v>47</v>
-      </c>
-      <c r="BN47" s="1" t="str">
+      <c r="BM47" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO47" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(47)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP47" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="48" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>0</v>
       </c>
@@ -11475,23 +11249,12 @@
       <c r="BL48" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM48">
-        <v>48</v>
-      </c>
-      <c r="BN48" s="1" t="str">
+      <c r="BM48" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO48" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(48)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP48" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="49" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>0</v>
       </c>
@@ -11684,23 +11447,12 @@
       <c r="BL49" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM49">
-        <v>49</v>
-      </c>
-      <c r="BN49" s="1" t="str">
+      <c r="BM49" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO49" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(49)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP49" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="50" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>0</v>
       </c>
@@ -11893,23 +11645,12 @@
       <c r="BL50" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM50">
-        <v>50</v>
-      </c>
-      <c r="BN50" s="1" t="str">
+      <c r="BM50" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO50" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(50)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP50" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="51" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>0</v>
       </c>
@@ -12102,23 +11843,12 @@
       <c r="BL51" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM51">
-        <v>51</v>
-      </c>
-      <c r="BN51" s="1" t="str">
+      <c r="BM51" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO51" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(51)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP51" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="52" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>0</v>
       </c>
@@ -12311,23 +12041,12 @@
       <c r="BL52" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM52">
-        <v>52</v>
-      </c>
-      <c r="BN52" s="1" t="str">
+      <c r="BM52" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO52" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(52)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP52" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="53" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>0</v>
       </c>
@@ -12520,23 +12239,12 @@
       <c r="BL53" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM53">
-        <v>53</v>
-      </c>
-      <c r="BN53" s="1" t="str">
+      <c r="BM53" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO53" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(53)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP53" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="54" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>0</v>
       </c>
@@ -12729,23 +12437,12 @@
       <c r="BL54" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM54">
-        <v>54</v>
-      </c>
-      <c r="BN54" s="1" t="str">
+      <c r="BM54" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO54" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(54)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP54" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="55" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>0</v>
       </c>
@@ -12938,23 +12635,12 @@
       <c r="BL55" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM55">
-        <v>55</v>
-      </c>
-      <c r="BN55" s="1" t="str">
+      <c r="BM55" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO55" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(55)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP55" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="56" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>0</v>
       </c>
@@ -13147,23 +12833,12 @@
       <c r="BL56" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM56">
-        <v>56</v>
-      </c>
-      <c r="BN56" s="1" t="str">
+      <c r="BM56" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO56" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(56)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP56" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="57" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>0</v>
       </c>
@@ -13356,23 +13031,12 @@
       <c r="BL57" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM57">
-        <v>57</v>
-      </c>
-      <c r="BN57" s="1" t="str">
+      <c r="BM57" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO57" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(57)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP57" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="58" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>0</v>
       </c>
@@ -13565,23 +13229,12 @@
       <c r="BL58" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM58">
-        <v>58</v>
-      </c>
-      <c r="BN58" s="1" t="str">
+      <c r="BM58" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO58" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(58)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP58" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="59" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>0</v>
       </c>
@@ -13774,23 +13427,12 @@
       <c r="BL59" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM59">
-        <v>59</v>
-      </c>
-      <c r="BN59" s="1" t="str">
+      <c r="BM59" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO59" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(59)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP59" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="60" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>0</v>
       </c>
@@ -13983,23 +13625,12 @@
       <c r="BL60" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM60">
-        <v>60</v>
-      </c>
-      <c r="BN60" s="1" t="str">
+      <c r="BM60" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO60" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(60)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP60" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="61" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>0</v>
       </c>
@@ -14192,23 +13823,12 @@
       <c r="BL61" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM61">
-        <v>61</v>
-      </c>
-      <c r="BN61" s="1" t="str">
+      <c r="BM61" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO61" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(61)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP61" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="62" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>0</v>
       </c>
@@ -14401,23 +14021,12 @@
       <c r="BL62" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM62">
-        <v>62</v>
-      </c>
-      <c r="BN62" s="1" t="str">
+      <c r="BM62" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO62" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(62)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP62" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="63" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>0</v>
       </c>
@@ -14610,23 +14219,12 @@
       <c r="BL63" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM63">
-        <v>63</v>
-      </c>
-      <c r="BN63" s="1" t="str">
+      <c r="BM63" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
-      <c r="BO63" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(63)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP63" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
-      </c>
     </row>
-    <row r="64" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>0</v>
       </c>
@@ -14819,141 +14417,161 @@
       <c r="BL64" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BM64">
-        <v>64</v>
-      </c>
-      <c r="BN64" s="1" t="str">
+      <c r="BM64" s="1" t="str">
         <f t="shared" si="0"/>
         <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
-      </c>
-      <c r="BO64" t="str">
-        <f t="shared" si="1"/>
-        <v>m$(64)="XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"</v>
-      </c>
-      <c r="BP64" t="str">
-        <f t="shared" si="2"/>
-        <v>{"XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX"},</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:BL64">
-    <cfRule type="containsText" dxfId="6" priority="7" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="9" priority="11" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH("X",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:BL1048576">
-    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
+      <formula>"G"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
+      <formula>"F"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="3" operator="equal">
+      <formula>"E"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="5" priority="5" operator="equal">
       <formula>"B"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
-      <formula>"H"</formula>
+    <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
+      <formula>"C"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="7" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="8" operator="equal">
       <formula>"D"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="9" operator="equal">
       <formula>"P"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="10" operator="equal">
       <formula>"W"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE5E0410-6B34-4610-813C-474405B474F7}">
-  <dimension ref="A2:D12"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="9.140625" style="5"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B1" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B2">
+        <v>15</v>
+      </c>
+      <c r="B2" s="5">
         <f>256*160*2/8</f>
         <v>10240</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3">
-        <f>64*64</f>
-        <v>4096</v>
+        <v>16</v>
+      </c>
+      <c r="B3" s="5">
+        <v>8192</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B4">
+        <v>53</v>
+      </c>
+      <c r="B4" s="5">
         <f>2*1024</f>
         <v>2048</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B5">
+        <v>54</v>
+      </c>
+      <c r="B5" s="5">
         <f>8*1024</f>
         <v>8192</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>56</v>
-      </c>
-      <c r="B6">
+        <v>55</v>
+      </c>
+      <c r="B6" s="5">
         <f>HEX2DEC("2000")</f>
         <v>8192</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>57</v>
-      </c>
-      <c r="B7">
+        <v>56</v>
+      </c>
+      <c r="B7" s="5">
         <v>4096</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>58</v>
-      </c>
-      <c r="B8">
+        <v>57</v>
+      </c>
+      <c r="B8" s="5">
         <v>1024</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10">
-        <f>SUM(B2:B8)</f>
-        <v>37888</v>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" s="5">
+        <f>1024*31</f>
+        <v>31744</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12">
-        <f>65536-B10</f>
-        <v>27648</v>
-      </c>
-      <c r="D12" s="4">
+        <v>17</v>
+      </c>
+      <c r="B12" s="5">
+        <f>SUM(B2:B8)</f>
+        <v>41984</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="5">
+        <f>65536-B12</f>
+        <v>23552</v>
+      </c>
+      <c r="C14" s="5">
         <f>B12/65536</f>
-        <v>0.421875</v>
+        <v>0.640625</v>
+      </c>
+      <c r="D14" s="4">
+        <f>B14/65536</f>
+        <v>0.359375</v>
       </c>
     </row>
   </sheetData>
@@ -14971,30 +14589,30 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J1" t="s">
         <v>44</v>
-      </c>
-      <c r="D1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F1" t="s">
-        <v>39</v>
-      </c>
-      <c r="G1" t="s">
-        <v>44</v>
-      </c>
-      <c r="H1" t="s">
-        <v>43</v>
-      </c>
-      <c r="J1" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B2">
         <v>16</v>
@@ -15021,7 +14639,7 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B3">
         <v>640</v>
@@ -15051,7 +14669,7 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B4">
         <v>20</v>
@@ -15083,27 +14701,27 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB40D263-C04C-4263-859C-02DFCB83777C}">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.140625" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B2">
         <v>130</v>
@@ -15119,27 +14737,27 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B3">
         <v>140</v>
       </c>
       <c r="C3" s="4">
-        <f t="shared" ref="C3:C9" si="0">(B3/$B$2)-1</f>
+        <f t="shared" ref="C3:C11" si="0">(B3/$B$2)-1</f>
         <v>7.6923076923076872E-2</v>
       </c>
       <c r="E3">
-        <f t="shared" ref="E3:E9" si="1">B3/40</f>
+        <f t="shared" ref="E3:E11" si="1">B3/40</f>
         <v>3.5</v>
       </c>
       <c r="F3">
-        <f t="shared" ref="F3:F9" si="2">E3/3</f>
+        <f t="shared" ref="F3:F11" si="2">E3/3</f>
         <v>1.1666666666666667</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B4">
         <v>360</v>
@@ -15159,7 +14777,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B5">
         <v>360</v>
@@ -15179,7 +14797,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B6">
         <v>630</v>
@@ -15199,7 +14817,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B7">
         <v>410</v>
@@ -15219,7 +14837,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B8">
         <v>530</v>
@@ -15239,7 +14857,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B9">
         <v>570</v>
@@ -15255,6 +14873,46 @@
       <c r="F9">
         <f t="shared" si="2"/>
         <v>4.75</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>99</v>
+      </c>
+      <c r="B10">
+        <v>600</v>
+      </c>
+      <c r="C10" s="4">
+        <f t="shared" si="0"/>
+        <v>3.615384615384615</v>
+      </c>
+      <c r="E10">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="F10">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>100</v>
+      </c>
+      <c r="B11">
+        <v>600</v>
+      </c>
+      <c r="C11" s="4">
+        <f t="shared" si="0"/>
+        <v>3.615384615384615</v>
+      </c>
+      <c r="E11">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="F11">
+        <f t="shared" si="2"/>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/Psion Levels.xlsx
+++ b/Psion Levels.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Zak\Documents\GitProjects\psion3d\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC656820-2D20-43AE-86B5-3FB7D5DA0A0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E2D3A58-E169-413D-8A55-5AF1EB1FDC50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{72A343FB-71F0-4738-BBFF-B23B40D170FF}"/>
   </bookViews>

--- a/Psion Levels.xlsx
+++ b/Psion Levels.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Zak\Documents\GitProjects\psion3d\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E2D3A58-E169-413D-8A55-5AF1EB1FDC50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{842CD905-0EE5-4695-9EA1-29933B55F2A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{72A343FB-71F0-4738-BBFF-B23B40D170FF}"/>
   </bookViews>

--- a/Psion Levels.xlsx
+++ b/Psion Levels.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Zak\Documents\GitProjects\psion3d\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{842CD905-0EE5-4695-9EA1-29933B55F2A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7440E436-38F8-4C02-8A4D-065CDC3A7715}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{72A343FB-71F0-4738-BBFF-B23B40D170FF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{72A343FB-71F0-4738-BBFF-B23B40D170FF}"/>
   </bookViews>
   <sheets>
     <sheet name="Mapbits" sheetId="4" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4227" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4238" uniqueCount="111">
   <si>
     <t>X</t>
   </si>
@@ -350,6 +350,36 @@
   <si>
     <t>U16 map</t>
   </si>
+  <si>
+    <t>Surprised</t>
+  </si>
+  <si>
+    <t>Delay</t>
+  </si>
+  <si>
+    <t>Aiming</t>
+  </si>
+  <si>
+    <t>Check if player is still in same position, if so shoot, else go to chase.</t>
+  </si>
+  <si>
+    <t>Hurt</t>
+  </si>
+  <si>
+    <t>When enemy has been hit</t>
+  </si>
+  <si>
+    <t>Evading</t>
+  </si>
+  <si>
+    <t>Go back to chase or evading</t>
+  </si>
+  <si>
+    <t>Move away from player</t>
+  </si>
+  <si>
+    <t>Move away from player or sidestep.</t>
+  </si>
 </sst>
 </file>
 
@@ -358,7 +388,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -376,6 +406,12 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Cascadia Code"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF569CD6"/>
+      <name val="Consolas"/>
       <family val="3"/>
     </font>
   </fonts>
@@ -399,7 +435,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -410,15 +446,18 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="10">
     <dxf>
       <fill>
         <patternFill>
@@ -497,67 +536,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFF00"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1097,7 +1075,7 @@
       <c r="A8">
         <v>9</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="8" t="s">
         <v>6</v>
       </c>
       <c r="G8">
@@ -1117,7 +1095,7 @@
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" s="6"/>
+      <c r="B9" s="8"/>
       <c r="G9">
         <v>8</v>
       </c>
@@ -1129,8 +1107,8 @@
       <c r="A10">
         <v>7</v>
       </c>
-      <c r="B10" s="6"/>
-      <c r="C10" s="7"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="6"/>
       <c r="G10">
         <v>9</v>
       </c>
@@ -1142,8 +1120,8 @@
       <c r="A11">
         <v>6</v>
       </c>
-      <c r="B11" s="6"/>
-      <c r="C11" s="7"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="6"/>
       <c r="G11">
         <v>10</v>
       </c>
@@ -1155,10 +1133,10 @@
       <c r="A12">
         <v>5</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C12" s="7"/>
+      <c r="C12" s="6"/>
       <c r="G12">
         <v>11</v>
       </c>
@@ -1170,8 +1148,8 @@
       <c r="A13">
         <v>4</v>
       </c>
-      <c r="B13" s="6"/>
-      <c r="C13" s="7"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="6"/>
       <c r="G13">
         <v>12</v>
       </c>
@@ -1183,8 +1161,8 @@
       <c r="A14">
         <v>3</v>
       </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="7"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="6"/>
       <c r="G14">
         <v>13</v>
       </c>
@@ -1196,8 +1174,8 @@
       <c r="A15">
         <v>2</v>
       </c>
-      <c r="B15" s="6"/>
-      <c r="C15" s="7"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="6"/>
       <c r="G15">
         <v>14</v>
       </c>
@@ -1209,8 +1187,8 @@
       <c r="A16">
         <v>1</v>
       </c>
-      <c r="B16" s="6"/>
-      <c r="C16" s="7"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="6"/>
       <c r="G16">
         <v>15</v>
       </c>
@@ -1222,8 +1200,8 @@
       <c r="A17">
         <v>0</v>
       </c>
-      <c r="B17" s="6"/>
-      <c r="C17" s="7"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1287,13 +1265,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1F75B1B-87D7-4382-913C-AEB74E49A06D}">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="68" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1327,13 +1305,10 @@
         <v>82</v>
       </c>
       <c r="D3" t="s">
-        <v>65</v>
+        <v>101</v>
       </c>
       <c r="E3" t="s">
-        <v>69</v>
-      </c>
-      <c r="F3" t="s">
-        <v>74</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1344,13 +1319,13 @@
         <v>83</v>
       </c>
       <c r="D4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -1361,10 +1336,13 @@
         <v>84</v>
       </c>
       <c r="D5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E5" t="s">
-        <v>72</v>
+        <v>70</v>
+      </c>
+      <c r="F5" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -1374,6 +1352,15 @@
       <c r="B6" t="s">
         <v>85</v>
       </c>
+      <c r="D6" t="s">
+        <v>103</v>
+      </c>
+      <c r="E6" t="s">
+        <v>102</v>
+      </c>
+      <c r="F6" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7">
@@ -1382,6 +1369,12 @@
       <c r="B7" t="s">
         <v>77</v>
       </c>
+      <c r="D7" t="s">
+        <v>67</v>
+      </c>
+      <c r="E7" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8">
@@ -1390,6 +1383,15 @@
       <c r="B8" t="s">
         <v>76</v>
       </c>
+      <c r="D8" t="s">
+        <v>105</v>
+      </c>
+      <c r="E8" t="s">
+        <v>106</v>
+      </c>
+      <c r="F8" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9">
@@ -1398,9 +1400,22 @@
       <c r="B9" t="s">
         <v>71</v>
       </c>
+      <c r="D9" t="s">
+        <v>107</v>
+      </c>
+      <c r="E9" t="s">
+        <v>109</v>
+      </c>
+      <c r="F9" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B15" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/Psion Levels.xlsx
+++ b/Psion Levels.xlsx
@@ -8,19 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Zak\Documents\GitProjects\psion3d\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7440E436-38F8-4C02-8A4D-065CDC3A7715}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FABBAF53-852A-4090-A617-543C6D400C02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{72A343FB-71F0-4738-BBFF-B23B40D170FF}"/>
+    <workbookView xWindow="1725" yWindow="2880" windowWidth="21600" windowHeight="11295" firstSheet="4" activeTab="9" xr2:uid="{72A343FB-71F0-4738-BBFF-B23B40D170FF}"/>
   </bookViews>
   <sheets>
     <sheet name="Mapbits" sheetId="4" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="9" r:id="rId2"/>
     <sheet name="AI States" sheetId="8" r:id="rId3"/>
     <sheet name="Tiles Type" sheetId="2" r:id="rId4"/>
-    <sheet name="Level 1" sheetId="1" r:id="rId5"/>
-    <sheet name="Memory Budget" sheetId="3" r:id="rId6"/>
-    <sheet name="Performance" sheetId="6" r:id="rId7"/>
-    <sheet name="Optimisation" sheetId="7" r:id="rId8"/>
+    <sheet name="Weapons" sheetId="10" r:id="rId5"/>
+    <sheet name="Level 1" sheetId="1" r:id="rId6"/>
+    <sheet name="Memory Budget" sheetId="3" r:id="rId7"/>
+    <sheet name="Performance" sheetId="6" r:id="rId8"/>
+    <sheet name="Optimisation" sheetId="7" r:id="rId9"/>
+    <sheet name="TIming" sheetId="11" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4238" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4254" uniqueCount="122">
   <si>
     <t>X</t>
   </si>
@@ -379,6 +381,39 @@
   </si>
   <si>
     <t>Move away from player or sidestep.</t>
+  </si>
+  <si>
+    <t>Pistol</t>
+  </si>
+  <si>
+    <t>SMG</t>
+  </si>
+  <si>
+    <t>AK47</t>
+  </si>
+  <si>
+    <t>LMG</t>
+  </si>
+  <si>
+    <t>Soldger</t>
+  </si>
+  <si>
+    <t>Player start</t>
+  </si>
+  <si>
+    <t>No 32bit div</t>
+  </si>
+  <si>
+    <t>Bare loop</t>
+  </si>
+  <si>
+    <t>FPS</t>
+  </si>
+  <si>
+    <t>MS</t>
+  </si>
+  <si>
+    <t>EMU</t>
   </si>
 </sst>
 </file>
@@ -1213,6 +1248,52 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F426B8BD-42FE-4B91-BDF5-11A7679F9A78}">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B1" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="E1" s="8"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5235E873-4701-4130-881C-1F333236149A}">
   <dimension ref="A1:B5"/>
@@ -1757,6 +1838,51 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DFE4376-F190-41D3-ACAB-06DF87696190}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="10.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{750D9AD9-7C84-4603-A2EE-1597D412FCF4}">
   <dimension ref="A1:BM64"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -14477,7 +14603,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE5E0410-6B34-4610-813C-474405B474F7}">
   <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -14594,7 +14720,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{692BE518-AAC1-41EE-AD19-DC91CDF8547C}">
   <dimension ref="A1:L4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -14639,9 +14765,12 @@
       <c r="F2">
         <v>630</v>
       </c>
+      <c r="G2">
+        <v>10</v>
+      </c>
       <c r="H2">
-        <f>1000/F2</f>
-        <v>1.5873015873015872</v>
+        <f>1000/G2</f>
+        <v>100</v>
       </c>
       <c r="J2">
         <f>F2/B2</f>
@@ -14669,9 +14798,12 @@
       <c r="F3">
         <v>790</v>
       </c>
+      <c r="G3">
+        <v>30</v>
+      </c>
       <c r="H3">
-        <f>1000/F3</f>
-        <v>1.2658227848101267</v>
+        <f>1000/G3</f>
+        <v>33.333333333333336</v>
       </c>
       <c r="J3">
         <f>F3/B3</f>
@@ -14714,9 +14846,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB40D263-C04C-4263-859C-02DFCB83777C}">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.7109375" bestFit="1" customWidth="1"/>
@@ -14758,15 +14890,15 @@
         <v>140</v>
       </c>
       <c r="C3" s="4">
-        <f t="shared" ref="C3:C11" si="0">(B3/$B$2)-1</f>
+        <f t="shared" ref="C3:C12" si="0">(B3/$B$2)-1</f>
         <v>7.6923076923076872E-2</v>
       </c>
       <c r="E3">
-        <f t="shared" ref="E3:E11" si="1">B3/40</f>
+        <f t="shared" ref="E3:E12" si="1">B3/40</f>
         <v>3.5</v>
       </c>
       <c r="F3">
-        <f t="shared" ref="F3:F11" si="2">E3/3</f>
+        <f t="shared" ref="F3:F12" si="2">E3/3</f>
         <v>1.1666666666666667</v>
       </c>
     </row>
@@ -14928,6 +15060,26 @@
       <c r="F11">
         <f t="shared" si="2"/>
         <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>117</v>
+      </c>
+      <c r="B12">
+        <v>610</v>
+      </c>
+      <c r="C12" s="4">
+        <f t="shared" si="0"/>
+        <v>3.6923076923076925</v>
+      </c>
+      <c r="E12">
+        <f t="shared" si="1"/>
+        <v>15.25</v>
+      </c>
+      <c r="F12">
+        <f t="shared" si="2"/>
+        <v>5.083333333333333</v>
       </c>
     </row>
   </sheetData>

--- a/Psion Levels.xlsx
+++ b/Psion Levels.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Zak\Documents\GitProjects\psion3d\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FABBAF53-852A-4090-A617-543C6D400C02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{037DF8B9-4D02-4B3C-8E4C-512A77B1E457}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1725" yWindow="2880" windowWidth="21600" windowHeight="11295" firstSheet="4" activeTab="9" xr2:uid="{72A343FB-71F0-4738-BBFF-B23B40D170FF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="9" xr2:uid="{72A343FB-71F0-4738-BBFF-B23B40D170FF}"/>
   </bookViews>
   <sheets>
     <sheet name="Mapbits" sheetId="4" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4254" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4265" uniqueCount="132">
   <si>
     <t>X</t>
   </si>
@@ -415,6 +415,36 @@
   <si>
     <t>EMU</t>
   </si>
+  <si>
+    <t>Update screen</t>
+  </si>
+  <si>
+    <t>sgcopy</t>
+  </si>
+  <si>
+    <t>Update Player</t>
+  </si>
+  <si>
+    <t>RunAI</t>
+  </si>
+  <si>
+    <t>ClrScreen</t>
+  </si>
+  <si>
+    <t>Draw</t>
+  </si>
+  <si>
+    <t>No Bricks</t>
+  </si>
+  <si>
+    <t>No wallX</t>
+  </si>
+  <si>
+    <t>All</t>
+  </si>
+  <si>
+    <t>Vid mem</t>
+  </si>
 </sst>
 </file>
 
@@ -470,7 +500,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -488,6 +518,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1250,13 +1281,15 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F426B8BD-42FE-4B91-BDF5-11A7679F9A78}">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" style="9"/>
+    <col min="5" max="5" width="9.140625" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B1" s="8" t="s">
         <v>121</v>
       </c>
@@ -1266,24 +1299,235 @@
       </c>
       <c r="E1" s="8"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>119</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="9" t="s">
         <v>120</v>
       </c>
       <c r="D2" t="s">
         <v>119</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="9" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>118</v>
       </c>
+      <c r="B3">
+        <v>32000</v>
+      </c>
+      <c r="C3" s="9">
+        <f>1000/B3</f>
+        <v>3.125E-2</v>
+      </c>
+      <c r="D3">
+        <v>13000</v>
+      </c>
+      <c r="E3" s="9">
+        <f>1000/D3</f>
+        <v>7.6923076923076927E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B4">
+        <v>17610</v>
+      </c>
+      <c r="C4" s="9">
+        <f>1000/B4</f>
+        <v>5.6785917092561047E-2</v>
+      </c>
+      <c r="D4">
+        <v>310</v>
+      </c>
+      <c r="E4" s="9">
+        <f>1000/D4</f>
+        <v>3.225806451612903</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>122</v>
+      </c>
+      <c r="B5">
+        <v>850</v>
+      </c>
+      <c r="C5" s="9">
+        <f>1000/B5</f>
+        <v>1.1764705882352942</v>
+      </c>
+      <c r="D5">
+        <v>32</v>
+      </c>
+      <c r="E5" s="9">
+        <f>1000/D5</f>
+        <v>31.25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B6">
+        <v>29000</v>
+      </c>
+      <c r="C6" s="9">
+        <f>1000/B6</f>
+        <v>3.4482758620689655E-2</v>
+      </c>
+      <c r="D6">
+        <v>12700</v>
+      </c>
+      <c r="E6" s="9">
+        <f>1000/D6</f>
+        <v>7.874015748031496E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>125</v>
+      </c>
+      <c r="B7">
+        <v>32000</v>
+      </c>
+      <c r="C7" s="9">
+        <f>1000/B7</f>
+        <v>3.125E-2</v>
+      </c>
+      <c r="D7">
+        <v>2406</v>
+      </c>
+      <c r="E7" s="9">
+        <f>1000/D7</f>
+        <v>0.41562759767248547</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>126</v>
+      </c>
+      <c r="B8">
+        <v>32000</v>
+      </c>
+      <c r="C8" s="9">
+        <f>1000/B8</f>
+        <v>3.125E-2</v>
+      </c>
+      <c r="D8">
+        <v>365</v>
+      </c>
+      <c r="E8" s="9">
+        <f>1000/D8</f>
+        <v>2.7397260273972601</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>127</v>
+      </c>
+      <c r="B9">
+        <v>2600</v>
+      </c>
+      <c r="C9" s="9">
+        <f>1000/B9</f>
+        <v>0.38461538461538464</v>
+      </c>
+      <c r="D9">
+        <v>22</v>
+      </c>
+      <c r="E9" s="9">
+        <f>1000/D9</f>
+        <v>45.454545454545453</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>128</v>
+      </c>
+      <c r="B10">
+        <v>2800</v>
+      </c>
+      <c r="C10" s="9">
+        <f>1000/B10</f>
+        <v>0.35714285714285715</v>
+      </c>
+      <c r="D10">
+        <v>24</v>
+      </c>
+      <c r="E10" s="9">
+        <f>1000/D10</f>
+        <v>41.666666666666664</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>129</v>
+      </c>
+      <c r="B11">
+        <v>3800</v>
+      </c>
+      <c r="C11" s="9">
+        <f>1000/B11</f>
+        <v>0.26315789473684209</v>
+      </c>
+      <c r="D11">
+        <v>38</v>
+      </c>
+      <c r="E11" s="9">
+        <f>1000/D11</f>
+        <v>26.315789473684209</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12">
+        <v>4562</v>
+      </c>
+      <c r="C12" s="9">
+        <f>1000/B12</f>
+        <v>0.21920210434020165</v>
+      </c>
+      <c r="D12">
+        <v>47</v>
+      </c>
+      <c r="E12" s="9">
+        <f>1000/D12</f>
+        <v>21.276595744680851</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>130</v>
+      </c>
+      <c r="D13">
+        <v>12</v>
+      </c>
+      <c r="E13" s="9">
+        <f>1000/D13</f>
+        <v>83.333333333333329</v>
+      </c>
+      <c r="G13" s="9"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>131</v>
+      </c>
+      <c r="D14">
+        <v>20</v>
+      </c>
+      <c r="E14" s="9">
+        <f>1000/D14</f>
+        <v>50</v>
+      </c>
+      <c r="F14" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/Psion Levels.xlsx
+++ b/Psion Levels.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Zak\Documents\GitProjects\psion3d\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{037DF8B9-4D02-4B3C-8E4C-512A77B1E457}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B937672-58F4-42C1-B078-036389BCACB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="9" xr2:uid="{72A343FB-71F0-4738-BBFF-B23B40D170FF}"/>
   </bookViews>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4265" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4268" uniqueCount="135">
   <si>
     <t>X</t>
   </si>
@@ -445,6 +445,15 @@
   <si>
     <t>Vid mem</t>
   </si>
+  <si>
+    <t>Packed Bitmap</t>
+  </si>
+  <si>
+    <t>Full Spriite</t>
+  </si>
+  <si>
+    <t>Clipped Sprite</t>
+  </si>
 </sst>
 </file>
 
@@ -515,10 +524,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1141,7 +1150,7 @@
       <c r="A8">
         <v>9</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="9" t="s">
         <v>6</v>
       </c>
       <c r="G8">
@@ -1161,7 +1170,7 @@
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" s="8"/>
+      <c r="B9" s="9"/>
       <c r="G9">
         <v>8</v>
       </c>
@@ -1173,7 +1182,7 @@
       <c r="A10">
         <v>7</v>
       </c>
-      <c r="B10" s="8"/>
+      <c r="B10" s="9"/>
       <c r="C10" s="6"/>
       <c r="G10">
         <v>9</v>
@@ -1186,7 +1195,7 @@
       <c r="A11">
         <v>6</v>
       </c>
-      <c r="B11" s="8"/>
+      <c r="B11" s="9"/>
       <c r="C11" s="6"/>
       <c r="G11">
         <v>10</v>
@@ -1199,7 +1208,7 @@
       <c r="A12">
         <v>5</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="9" t="s">
         <v>31</v>
       </c>
       <c r="C12" s="6"/>
@@ -1214,7 +1223,7 @@
       <c r="A13">
         <v>4</v>
       </c>
-      <c r="B13" s="8"/>
+      <c r="B13" s="9"/>
       <c r="C13" s="6"/>
       <c r="G13">
         <v>12</v>
@@ -1227,7 +1236,7 @@
       <c r="A14">
         <v>3</v>
       </c>
-      <c r="B14" s="8"/>
+      <c r="B14" s="9"/>
       <c r="C14" s="6"/>
       <c r="G14">
         <v>13</v>
@@ -1240,7 +1249,7 @@
       <c r="A15">
         <v>2</v>
       </c>
-      <c r="B15" s="8"/>
+      <c r="B15" s="9"/>
       <c r="C15" s="6"/>
       <c r="G15">
         <v>14</v>
@@ -1253,7 +1262,7 @@
       <c r="A16">
         <v>1</v>
       </c>
-      <c r="B16" s="8"/>
+      <c r="B16" s="9"/>
       <c r="C16" s="6"/>
       <c r="G16">
         <v>15</v>
@@ -1266,7 +1275,7 @@
       <c r="A17">
         <v>0</v>
       </c>
-      <c r="B17" s="8"/>
+      <c r="B17" s="9"/>
       <c r="C17" s="6"/>
     </row>
   </sheetData>
@@ -1281,35 +1290,35 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F426B8BD-42FE-4B91-BDF5-11A7679F9A78}">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.140625" style="9"/>
-    <col min="5" max="5" width="9.140625" style="9"/>
+    <col min="3" max="3" width="9.140625" style="8"/>
+    <col min="5" max="5" width="9.140625" style="8"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8" t="s">
+      <c r="C1" s="9"/>
+      <c r="D1" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="E1" s="8"/>
+      <c r="E1" s="9"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>119</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="8" t="s">
         <v>120</v>
       </c>
       <c r="D2" t="s">
         <v>119</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="8" t="s">
         <v>120</v>
       </c>
     </row>
@@ -1320,15 +1329,15 @@
       <c r="B3">
         <v>32000</v>
       </c>
-      <c r="C3" s="9">
-        <f>1000/B3</f>
+      <c r="C3" s="8">
+        <f t="shared" ref="C3:C12" si="0">1000/B3</f>
         <v>3.125E-2</v>
       </c>
       <c r="D3">
         <v>13000</v>
       </c>
-      <c r="E3" s="9">
-        <f>1000/D3</f>
+      <c r="E3" s="8">
+        <f t="shared" ref="E3:E17" si="1">1000/D3</f>
         <v>7.6923076923076927E-2</v>
       </c>
     </row>
@@ -1339,16 +1348,20 @@
       <c r="B4">
         <v>17610</v>
       </c>
-      <c r="C4" s="9">
-        <f>1000/B4</f>
+      <c r="C4" s="8">
+        <f t="shared" si="0"/>
         <v>5.6785917092561047E-2</v>
       </c>
       <c r="D4">
         <v>310</v>
       </c>
-      <c r="E4" s="9">
-        <f>1000/D4</f>
+      <c r="E4" s="8">
+        <f t="shared" si="1"/>
         <v>3.225806451612903</v>
+      </c>
+      <c r="F4" s="8">
+        <f>E4-E3</f>
+        <v>3.1488833746898259</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -1358,16 +1371,20 @@
       <c r="B5">
         <v>850</v>
       </c>
-      <c r="C5" s="9">
-        <f>1000/B5</f>
+      <c r="C5" s="8">
+        <f t="shared" si="0"/>
         <v>1.1764705882352942</v>
       </c>
       <c r="D5">
         <v>32</v>
       </c>
-      <c r="E5" s="9">
-        <f>1000/D5</f>
+      <c r="E5" s="8">
+        <f t="shared" si="1"/>
         <v>31.25</v>
+      </c>
+      <c r="F5" s="8">
+        <f>E5-(E4+E3)</f>
+        <v>27.947270471464019</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -1377,16 +1394,20 @@
       <c r="B6">
         <v>29000</v>
       </c>
-      <c r="C6" s="9">
-        <f>1000/B6</f>
+      <c r="C6" s="8">
+        <f t="shared" si="0"/>
         <v>3.4482758620689655E-2</v>
       </c>
       <c r="D6">
         <v>12700</v>
       </c>
-      <c r="E6" s="9">
-        <f>1000/D6</f>
+      <c r="E6" s="8">
+        <f t="shared" si="1"/>
         <v>7.874015748031496E-2</v>
+      </c>
+      <c r="F6" s="8">
+        <f>E6-E3</f>
+        <v>1.8170805572380322E-3</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -1396,16 +1417,20 @@
       <c r="B7">
         <v>32000</v>
       </c>
-      <c r="C7" s="9">
-        <f>1000/B7</f>
+      <c r="C7" s="8">
+        <f t="shared" si="0"/>
         <v>3.125E-2</v>
       </c>
       <c r="D7">
         <v>2406</v>
       </c>
-      <c r="E7" s="9">
-        <f>1000/D7</f>
+      <c r="E7" s="8">
+        <f t="shared" si="1"/>
         <v>0.41562759767248547</v>
+      </c>
+      <c r="F7" s="8">
+        <f>E7-E3</f>
+        <v>0.33870452074940854</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -1415,16 +1440,20 @@
       <c r="B8">
         <v>32000</v>
       </c>
-      <c r="C8" s="9">
-        <f>1000/B8</f>
+      <c r="C8" s="8">
+        <f t="shared" si="0"/>
         <v>3.125E-2</v>
       </c>
       <c r="D8">
         <v>365</v>
       </c>
-      <c r="E8" s="9">
-        <f>1000/D8</f>
+      <c r="E8" s="8">
+        <f t="shared" si="1"/>
         <v>2.7397260273972601</v>
+      </c>
+      <c r="F8" s="8">
+        <f>E8-E3</f>
+        <v>2.662802950474183</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -1434,17 +1463,22 @@
       <c r="B9">
         <v>2600</v>
       </c>
-      <c r="C9" s="9">
-        <f>1000/B9</f>
+      <c r="C9" s="8">
+        <f t="shared" si="0"/>
         <v>0.38461538461538464</v>
       </c>
       <c r="D9">
         <v>22</v>
       </c>
-      <c r="E9" s="9">
-        <f>1000/D9</f>
+      <c r="E9" s="8">
+        <f t="shared" si="1"/>
         <v>45.454545454545453</v>
       </c>
+      <c r="F9" s="8">
+        <f>E9-(E4+E3)</f>
+        <v>42.151815926009476</v>
+      </c>
+      <c r="G9" s="8"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
@@ -1453,16 +1487,20 @@
       <c r="B10">
         <v>2800</v>
       </c>
-      <c r="C10" s="9">
-        <f>1000/B10</f>
+      <c r="C10" s="8">
+        <f t="shared" si="0"/>
         <v>0.35714285714285715</v>
       </c>
       <c r="D10">
         <v>24</v>
       </c>
-      <c r="E10" s="9">
-        <f>1000/D10</f>
+      <c r="E10" s="8">
+        <f t="shared" si="1"/>
         <v>41.666666666666664</v>
+      </c>
+      <c r="F10" s="8">
+        <f>E9-E10</f>
+        <v>3.787878787878789</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -1472,16 +1510,20 @@
       <c r="B11">
         <v>3800</v>
       </c>
-      <c r="C11" s="9">
-        <f>1000/B11</f>
+      <c r="C11" s="8">
+        <f t="shared" si="0"/>
         <v>0.26315789473684209</v>
       </c>
       <c r="D11">
         <v>38</v>
       </c>
-      <c r="E11" s="9">
-        <f>1000/D11</f>
+      <c r="E11" s="8">
+        <f t="shared" si="1"/>
         <v>26.315789473684209</v>
+      </c>
+      <c r="F11" s="8">
+        <f>E9-E11</f>
+        <v>19.138755980861244</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -1491,16 +1533,20 @@
       <c r="B12">
         <v>4562</v>
       </c>
-      <c r="C12" s="9">
-        <f>1000/B12</f>
+      <c r="C12" s="8">
+        <f t="shared" si="0"/>
         <v>0.21920210434020165</v>
       </c>
       <c r="D12">
         <v>47</v>
       </c>
-      <c r="E12" s="9">
-        <f>1000/D12</f>
+      <c r="E12" s="8">
+        <f t="shared" si="1"/>
         <v>21.276595744680851</v>
+      </c>
+      <c r="F12" s="8">
+        <f>E9-E12</f>
+        <v>24.177949709864603</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -1510,11 +1556,11 @@
       <c r="D13">
         <v>12</v>
       </c>
-      <c r="E13" s="9">
-        <f>1000/D13</f>
+      <c r="E13" s="8">
+        <f t="shared" si="1"/>
         <v>83.333333333333329</v>
       </c>
-      <c r="G13" s="9"/>
+      <c r="G13" s="8"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
@@ -1523,11 +1569,51 @@
       <c r="D14">
         <v>20</v>
       </c>
-      <c r="E14" s="9">
-        <f>1000/D14</f>
+      <c r="E14" s="8">
+        <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="F14" s="9"/>
+      <c r="F14" s="8"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>132</v>
+      </c>
+      <c r="D15">
+        <v>23</v>
+      </c>
+      <c r="E15" s="8">
+        <f t="shared" si="1"/>
+        <v>43.478260869565219</v>
+      </c>
+      <c r="F15" s="8">
+        <f>E15-E14</f>
+        <v>-6.5217391304347814</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>133</v>
+      </c>
+      <c r="D16">
+        <v>14</v>
+      </c>
+      <c r="E16" s="8">
+        <f t="shared" si="1"/>
+        <v>71.428571428571431</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>134</v>
+      </c>
+      <c r="D17">
+        <v>16</v>
+      </c>
+      <c r="E17" s="8">
+        <f t="shared" si="1"/>
+        <v>62.5</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/Psion Levels.xlsx
+++ b/Psion Levels.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Zak\Documents\GitProjects\psion3d\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B937672-58F4-42C1-B078-036389BCACB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF58968A-54D1-4D2A-A357-F175810711C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="9" xr2:uid="{72A343FB-71F0-4738-BBFF-B23B40D170FF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="5" activeTab="7" xr2:uid="{72A343FB-71F0-4738-BBFF-B23B40D170FF}"/>
   </bookViews>
   <sheets>
     <sheet name="Mapbits" sheetId="4" r:id="rId1"/>
@@ -20,8 +20,8 @@
     <sheet name="Weapons" sheetId="10" r:id="rId5"/>
     <sheet name="Level 1" sheetId="1" r:id="rId6"/>
     <sheet name="Memory Budget" sheetId="3" r:id="rId7"/>
-    <sheet name="Performance" sheetId="6" r:id="rId8"/>
-    <sheet name="Optimisation" sheetId="7" r:id="rId9"/>
+    <sheet name="Optimisation" sheetId="7" r:id="rId8"/>
+    <sheet name="Performance" sheetId="6" r:id="rId9"/>
     <sheet name="TIming" sheetId="11" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4268" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4268" uniqueCount="134">
   <si>
     <t>X</t>
   </si>
@@ -419,9 +419,6 @@
     <t>Update screen</t>
   </si>
   <si>
-    <t>sgcopy</t>
-  </si>
-  <si>
     <t>Update Player</t>
   </si>
   <si>
@@ -443,24 +440,25 @@
     <t>All</t>
   </si>
   <si>
-    <t>Vid mem</t>
+    <t>No Sprites</t>
   </si>
   <si>
-    <t>Packed Bitmap</t>
+    <t>No Gun</t>
   </si>
   <si>
-    <t>Full Spriite</t>
+    <t>Optimised Spr</t>
   </si>
   <si>
-    <t>Clipped Sprite</t>
+    <t>Gun sprite</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="#,##0.0"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -509,7 +507,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -525,6 +523,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1150,7 +1149,7 @@
       <c r="A8">
         <v>9</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="10" t="s">
         <v>6</v>
       </c>
       <c r="G8">
@@ -1170,7 +1169,7 @@
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" s="9"/>
+      <c r="B9" s="10"/>
       <c r="G9">
         <v>8</v>
       </c>
@@ -1182,7 +1181,7 @@
       <c r="A10">
         <v>7</v>
       </c>
-      <c r="B10" s="9"/>
+      <c r="B10" s="10"/>
       <c r="C10" s="6"/>
       <c r="G10">
         <v>9</v>
@@ -1195,7 +1194,7 @@
       <c r="A11">
         <v>6</v>
       </c>
-      <c r="B11" s="9"/>
+      <c r="B11" s="10"/>
       <c r="C11" s="6"/>
       <c r="G11">
         <v>10</v>
@@ -1208,7 +1207,7 @@
       <c r="A12">
         <v>5</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="10" t="s">
         <v>31</v>
       </c>
       <c r="C12" s="6"/>
@@ -1223,7 +1222,7 @@
       <c r="A13">
         <v>4</v>
       </c>
-      <c r="B13" s="9"/>
+      <c r="B13" s="10"/>
       <c r="C13" s="6"/>
       <c r="G13">
         <v>12</v>
@@ -1236,7 +1235,7 @@
       <c r="A14">
         <v>3</v>
       </c>
-      <c r="B14" s="9"/>
+      <c r="B14" s="10"/>
       <c r="C14" s="6"/>
       <c r="G14">
         <v>13</v>
@@ -1249,7 +1248,7 @@
       <c r="A15">
         <v>2</v>
       </c>
-      <c r="B15" s="9"/>
+      <c r="B15" s="10"/>
       <c r="C15" s="6"/>
       <c r="G15">
         <v>14</v>
@@ -1262,7 +1261,7 @@
       <c r="A16">
         <v>1</v>
       </c>
-      <c r="B16" s="9"/>
+      <c r="B16" s="10"/>
       <c r="C16" s="6"/>
       <c r="G16">
         <v>15</v>
@@ -1275,7 +1274,7 @@
       <c r="A17">
         <v>0</v>
       </c>
-      <c r="B17" s="9"/>
+      <c r="B17" s="10"/>
       <c r="C17" s="6"/>
     </row>
   </sheetData>
@@ -1290,25 +1289,27 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F426B8BD-42FE-4B91-BDF5-11A7679F9A78}">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.140625" style="8"/>
     <col min="5" max="5" width="9.140625" style="8"/>
+    <col min="7" max="7" width="9.140625" style="9"/>
+    <col min="8" max="8" width="9.140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B1" s="9" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B1" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9" t="s">
+      <c r="C1" s="10"/>
+      <c r="D1" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="E1" s="9"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E1" s="10"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>119</v>
       </c>
@@ -1322,7 +1323,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>118</v>
       </c>
@@ -1330,87 +1331,99 @@
         <v>32000</v>
       </c>
       <c r="C3" s="8">
-        <f t="shared" ref="C3:C12" si="0">1000/B3</f>
+        <f t="shared" ref="C3:C11" si="0">1000/B3</f>
         <v>3.125E-2</v>
       </c>
       <c r="D3">
-        <v>13000</v>
+        <v>17000</v>
       </c>
       <c r="E3" s="8">
-        <f t="shared" ref="E3:E17" si="1">1000/D3</f>
-        <v>7.6923076923076927E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+        <f t="shared" ref="E3:E15" si="1">1000/D3</f>
+        <v>5.8823529411764705E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B4">
-        <v>17610</v>
+        <v>850</v>
       </c>
       <c r="C4" s="8">
         <f t="shared" si="0"/>
-        <v>5.6785917092561047E-2</v>
+        <v>1.1764705882352942</v>
       </c>
       <c r="D4">
-        <v>310</v>
+        <v>264</v>
       </c>
       <c r="E4" s="8">
         <f t="shared" si="1"/>
-        <v>3.225806451612903</v>
+        <v>3.7878787878787881</v>
       </c>
       <c r="F4" s="8">
         <f>E4-E3</f>
-        <v>3.1488833746898259</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+        <v>3.7290552584670236</v>
+      </c>
+      <c r="G4" s="9">
+        <f>1000/F4</f>
+        <v>268.16443594646267</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B5">
-        <v>850</v>
+        <v>29000</v>
       </c>
       <c r="C5" s="8">
         <f t="shared" si="0"/>
-        <v>1.1764705882352942</v>
+        <v>3.4482758620689655E-2</v>
       </c>
       <c r="D5">
-        <v>32</v>
+        <v>10790</v>
       </c>
       <c r="E5" s="8">
         <f t="shared" si="1"/>
-        <v>31.25</v>
+        <v>9.2678405931417976E-2</v>
       </c>
       <c r="F5" s="8">
-        <f>E5-(E4+E3)</f>
-        <v>27.947270471464019</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+        <f>E5-E3</f>
+        <v>3.3854876519653271E-2</v>
+      </c>
+      <c r="G5" s="9">
+        <f t="shared" ref="G5:G13" si="2">1000/F5</f>
+        <v>29537.842190016105</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>124</v>
       </c>
       <c r="B6">
-        <v>29000</v>
+        <v>32000</v>
       </c>
       <c r="C6" s="8">
         <f t="shared" si="0"/>
-        <v>3.4482758620689655E-2</v>
+        <v>3.125E-2</v>
       </c>
       <c r="D6">
-        <v>12700</v>
+        <v>10600</v>
       </c>
       <c r="E6" s="8">
         <f t="shared" si="1"/>
-        <v>7.874015748031496E-2</v>
+        <v>9.4339622641509441E-2</v>
       </c>
       <c r="F6" s="8">
         <f>E6-E3</f>
-        <v>1.8170805572380322E-3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+        <v>3.5516093229744736E-2</v>
+      </c>
+      <c r="G6" s="9">
+        <f t="shared" si="2"/>
+        <v>28156.249999999993</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>125</v>
       </c>
@@ -1422,197 +1435,195 @@
         <v>3.125E-2</v>
       </c>
       <c r="D7">
-        <v>2406</v>
+        <v>235</v>
       </c>
       <c r="E7" s="8">
         <f t="shared" si="1"/>
-        <v>0.41562759767248547</v>
+        <v>4.2553191489361701</v>
       </c>
       <c r="F7" s="8">
         <f>E7-E3</f>
-        <v>0.33870452074940854</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+        <v>4.1964956195244056</v>
+      </c>
+      <c r="G7" s="9">
+        <f t="shared" si="2"/>
+        <v>238.29406501640321</v>
+      </c>
+      <c r="H7" s="4">
+        <f>F7/E14</f>
+        <v>3.3571964956195244E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>126</v>
       </c>
       <c r="B8">
-        <v>32000</v>
+        <v>2600</v>
       </c>
       <c r="C8" s="8">
         <f t="shared" si="0"/>
-        <v>3.125E-2</v>
+        <v>0.38461538461538464</v>
       </c>
       <c r="D8">
-        <v>365</v>
+        <v>9</v>
       </c>
       <c r="E8" s="8">
         <f t="shared" si="1"/>
-        <v>2.7397260273972601</v>
+        <v>111.11111111111111</v>
       </c>
       <c r="F8" s="8">
         <f>E8-E3</f>
-        <v>2.662802950474183</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+        <v>111.05228758169935</v>
+      </c>
+      <c r="G8" s="9">
+        <f t="shared" si="2"/>
+        <v>9.0047672297098469</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>127</v>
       </c>
       <c r="B9">
-        <v>2600</v>
+        <v>2800</v>
       </c>
       <c r="C9" s="8">
         <f t="shared" si="0"/>
-        <v>0.38461538461538464</v>
+        <v>0.35714285714285715</v>
       </c>
       <c r="D9">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E9" s="8">
         <f t="shared" si="1"/>
-        <v>45.454545454545453</v>
+        <v>111.11111111111111</v>
       </c>
       <c r="F9" s="8">
-        <f>E9-(E4+E3)</f>
-        <v>42.151815926009476</v>
-      </c>
-      <c r="G9" s="8"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+        <f>E9-E8</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>128</v>
       </c>
       <c r="B10">
-        <v>2800</v>
+        <v>3800</v>
       </c>
       <c r="C10" s="8">
         <f t="shared" si="0"/>
-        <v>0.35714285714285715</v>
+        <v>0.26315789473684209</v>
       </c>
       <c r="D10">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="E10" s="8">
         <f t="shared" si="1"/>
-        <v>41.666666666666664</v>
+        <v>90.909090909090907</v>
       </c>
       <c r="F10" s="8">
-        <f>E9-E10</f>
-        <v>3.787878787878789</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+        <f>E8-E10</f>
+        <v>20.202020202020208</v>
+      </c>
+      <c r="G10" s="9">
+        <f t="shared" si="2"/>
+        <v>49.499999999999986</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>129</v>
+        <v>41</v>
       </c>
       <c r="B11">
-        <v>3800</v>
+        <v>4562</v>
       </c>
       <c r="C11" s="8">
         <f t="shared" si="0"/>
-        <v>0.26315789473684209</v>
+        <v>0.21920210434020165</v>
       </c>
       <c r="D11">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="E11" s="8">
         <f t="shared" si="1"/>
-        <v>26.315789473684209</v>
+        <v>83.333333333333329</v>
       </c>
       <c r="F11" s="8">
-        <f>E9-E11</f>
-        <v>19.138755980861244</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+        <f>E8-E11</f>
+        <v>27.777777777777786</v>
+      </c>
+      <c r="G11" s="9">
+        <f t="shared" si="2"/>
+        <v>35.999999999999993</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>41</v>
-      </c>
-      <c r="B12">
-        <v>4562</v>
-      </c>
-      <c r="C12" s="8">
-        <f t="shared" si="0"/>
-        <v>0.21920210434020165</v>
+        <v>130</v>
       </c>
       <c r="D12">
-        <v>47</v>
+        <v>9</v>
       </c>
       <c r="E12" s="8">
         <f t="shared" si="1"/>
-        <v>21.276595744680851</v>
+        <v>111.11111111111111</v>
       </c>
       <c r="F12" s="8">
-        <f>E9-E12</f>
-        <v>24.177949709864603</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+        <f>E12-E8</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D13">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E13" s="8">
         <f t="shared" si="1"/>
-        <v>83.333333333333329</v>
-      </c>
-      <c r="G13" s="8"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+        <v>66.666666666666671</v>
+      </c>
+      <c r="F13" s="8">
+        <f>E8-E13</f>
+        <v>44.444444444444443</v>
+      </c>
+      <c r="G13" s="9">
+        <f t="shared" si="2"/>
+        <v>22.5</v>
+      </c>
+      <c r="H13" s="4">
+        <f>F13/E14</f>
+        <v>0.35555555555555557</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D14">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E14" s="8">
         <f t="shared" si="1"/>
-        <v>50</v>
-      </c>
-      <c r="F14" s="8"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>132</v>
       </c>
       <c r="D15">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E15" s="8">
         <f t="shared" si="1"/>
-        <v>43.478260869565219</v>
+        <v>90.909090909090907</v>
       </c>
       <c r="F15" s="8">
-        <f>E15-E14</f>
-        <v>-6.5217391304347814</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>133</v>
-      </c>
-      <c r="D16">
-        <v>14</v>
-      </c>
-      <c r="E16" s="8">
-        <f t="shared" si="1"/>
-        <v>71.428571428571431</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>134</v>
-      </c>
-      <c r="D17">
-        <v>16</v>
-      </c>
-      <c r="E17" s="8">
-        <f t="shared" si="1"/>
-        <v>62.5</v>
+        <f>E8-E15</f>
+        <v>20.202020202020208</v>
       </c>
     </row>
   </sheetData>
@@ -15027,6 +15038,14 @@
         <f>SUM(B2:B8)</f>
         <v>41984</v>
       </c>
+      <c r="C12" s="5">
+        <f>SUM(C9:C11)</f>
+        <v>31744</v>
+      </c>
+      <c r="D12" s="5">
+        <f>SUM(B12:C12)</f>
+        <v>73728</v>
+      </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
@@ -15051,6 +15070,271 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB40D263-C04C-4263-859C-02DFCB83777C}">
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2">
+        <v>130</v>
+      </c>
+      <c r="E2">
+        <f>B2/40</f>
+        <v>3.25</v>
+      </c>
+      <c r="F2">
+        <f>E2/3</f>
+        <v>1.0833333333333333</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3">
+        <v>140</v>
+      </c>
+      <c r="C3" s="4">
+        <f t="shared" ref="C3:C12" si="0">(B3/$B$2)-1</f>
+        <v>7.6923076923076872E-2</v>
+      </c>
+      <c r="E3">
+        <f t="shared" ref="E3:E12" si="1">B3/40</f>
+        <v>3.5</v>
+      </c>
+      <c r="F3">
+        <f t="shared" ref="F3:F14" si="2">E3/3</f>
+        <v>1.1666666666666667</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4">
+        <v>360</v>
+      </c>
+      <c r="C4" s="4">
+        <f t="shared" si="0"/>
+        <v>1.7692307692307692</v>
+      </c>
+      <c r="E4">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="F4">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B5">
+        <v>360</v>
+      </c>
+      <c r="C5" s="4">
+        <f t="shared" si="0"/>
+        <v>1.7692307692307692</v>
+      </c>
+      <c r="E5">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="F5">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B6">
+        <v>630</v>
+      </c>
+      <c r="C6" s="4">
+        <f t="shared" si="0"/>
+        <v>3.8461538461538458</v>
+      </c>
+      <c r="E6">
+        <f t="shared" si="1"/>
+        <v>15.75</v>
+      </c>
+      <c r="F6">
+        <f t="shared" si="2"/>
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B7">
+        <v>410</v>
+      </c>
+      <c r="C7" s="4">
+        <f t="shared" si="0"/>
+        <v>2.1538461538461537</v>
+      </c>
+      <c r="E7">
+        <f t="shared" si="1"/>
+        <v>10.25</v>
+      </c>
+      <c r="F7">
+        <f t="shared" si="2"/>
+        <v>3.4166666666666665</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>52</v>
+      </c>
+      <c r="B8">
+        <v>530</v>
+      </c>
+      <c r="C8" s="4">
+        <f t="shared" si="0"/>
+        <v>3.0769230769230766</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="1"/>
+        <v>13.25</v>
+      </c>
+      <c r="F8">
+        <f t="shared" si="2"/>
+        <v>4.416666666666667</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B9">
+        <v>570</v>
+      </c>
+      <c r="C9" s="4">
+        <f t="shared" si="0"/>
+        <v>3.384615384615385</v>
+      </c>
+      <c r="E9">
+        <f t="shared" si="1"/>
+        <v>14.25</v>
+      </c>
+      <c r="F9">
+        <f t="shared" si="2"/>
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>99</v>
+      </c>
+      <c r="B10">
+        <v>600</v>
+      </c>
+      <c r="C10" s="4">
+        <f t="shared" si="0"/>
+        <v>3.615384615384615</v>
+      </c>
+      <c r="E10">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="F10">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>100</v>
+      </c>
+      <c r="B11">
+        <v>600</v>
+      </c>
+      <c r="C11" s="4">
+        <f t="shared" si="0"/>
+        <v>3.615384615384615</v>
+      </c>
+      <c r="E11">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="F11">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>117</v>
+      </c>
+      <c r="B12">
+        <v>610</v>
+      </c>
+      <c r="C12" s="4">
+        <f t="shared" si="0"/>
+        <v>3.6923076923076925</v>
+      </c>
+      <c r="E12">
+        <f t="shared" si="1"/>
+        <v>15.25</v>
+      </c>
+      <c r="F12">
+        <f t="shared" si="2"/>
+        <v>5.083333333333333</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>133</v>
+      </c>
+      <c r="E13">
+        <v>8</v>
+      </c>
+      <c r="F13">
+        <f t="shared" si="2"/>
+        <v>2.6666666666666665</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E14">
+        <v>11</v>
+      </c>
+      <c r="F14">
+        <f t="shared" si="2"/>
+        <v>3.6666666666666665</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{692BE518-AAC1-41EE-AD19-DC91CDF8547C}">
   <dimension ref="A1:L4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -15174,245 +15458,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB40D263-C04C-4263-859C-02DFCB83777C}">
-  <dimension ref="A1:F12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.140625" style="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B2">
-        <v>130</v>
-      </c>
-      <c r="E2">
-        <f>B2/40</f>
-        <v>3.25</v>
-      </c>
-      <c r="F2">
-        <f>E2/3</f>
-        <v>1.0833333333333333</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B3">
-        <v>140</v>
-      </c>
-      <c r="C3" s="4">
-        <f t="shared" ref="C3:C12" si="0">(B3/$B$2)-1</f>
-        <v>7.6923076923076872E-2</v>
-      </c>
-      <c r="E3">
-        <f t="shared" ref="E3:E12" si="1">B3/40</f>
-        <v>3.5</v>
-      </c>
-      <c r="F3">
-        <f t="shared" ref="F3:F12" si="2">E3/3</f>
-        <v>1.1666666666666667</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B4">
-        <v>360</v>
-      </c>
-      <c r="C4" s="4">
-        <f t="shared" si="0"/>
-        <v>1.7692307692307692</v>
-      </c>
-      <c r="E4">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="F4">
-        <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B5">
-        <v>360</v>
-      </c>
-      <c r="C5" s="4">
-        <f t="shared" si="0"/>
-        <v>1.7692307692307692</v>
-      </c>
-      <c r="E5">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="F5">
-        <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B6">
-        <v>630</v>
-      </c>
-      <c r="C6" s="4">
-        <f t="shared" si="0"/>
-        <v>3.8461538461538458</v>
-      </c>
-      <c r="E6">
-        <f t="shared" si="1"/>
-        <v>15.75</v>
-      </c>
-      <c r="F6">
-        <f t="shared" si="2"/>
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>51</v>
-      </c>
-      <c r="B7">
-        <v>410</v>
-      </c>
-      <c r="C7" s="4">
-        <f t="shared" si="0"/>
-        <v>2.1538461538461537</v>
-      </c>
-      <c r="E7">
-        <f t="shared" si="1"/>
-        <v>10.25</v>
-      </c>
-      <c r="F7">
-        <f t="shared" si="2"/>
-        <v>3.4166666666666665</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>52</v>
-      </c>
-      <c r="B8">
-        <v>530</v>
-      </c>
-      <c r="C8" s="4">
-        <f t="shared" si="0"/>
-        <v>3.0769230769230766</v>
-      </c>
-      <c r="E8">
-        <f t="shared" si="1"/>
-        <v>13.25</v>
-      </c>
-      <c r="F8">
-        <f t="shared" si="2"/>
-        <v>4.416666666666667</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>52</v>
-      </c>
-      <c r="B9">
-        <v>570</v>
-      </c>
-      <c r="C9" s="4">
-        <f t="shared" si="0"/>
-        <v>3.384615384615385</v>
-      </c>
-      <c r="E9">
-        <f t="shared" si="1"/>
-        <v>14.25</v>
-      </c>
-      <c r="F9">
-        <f t="shared" si="2"/>
-        <v>4.75</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>99</v>
-      </c>
-      <c r="B10">
-        <v>600</v>
-      </c>
-      <c r="C10" s="4">
-        <f t="shared" si="0"/>
-        <v>3.615384615384615</v>
-      </c>
-      <c r="E10">
-        <f t="shared" si="1"/>
-        <v>15</v>
-      </c>
-      <c r="F10">
-        <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>100</v>
-      </c>
-      <c r="B11">
-        <v>600</v>
-      </c>
-      <c r="C11" s="4">
-        <f t="shared" si="0"/>
-        <v>3.615384615384615</v>
-      </c>
-      <c r="E11">
-        <f t="shared" si="1"/>
-        <v>15</v>
-      </c>
-      <c r="F11">
-        <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>117</v>
-      </c>
-      <c r="B12">
-        <v>610</v>
-      </c>
-      <c r="C12" s="4">
-        <f t="shared" si="0"/>
-        <v>3.6923076923076925</v>
-      </c>
-      <c r="E12">
-        <f t="shared" si="1"/>
-        <v>15.25</v>
-      </c>
-      <c r="F12">
-        <f t="shared" si="2"/>
-        <v>5.083333333333333</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/Psion Levels.xlsx
+++ b/Psion Levels.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Zak\Documents\GitProjects\psion3d\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF58968A-54D1-4D2A-A357-F175810711C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9905EA7A-F998-4A46-BFEF-D3F687D7BECB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="5" activeTab="7" xr2:uid="{72A343FB-71F0-4738-BBFF-B23B40D170FF}"/>
   </bookViews>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4268" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4269" uniqueCount="135">
   <si>
     <t>X</t>
   </si>
@@ -450,6 +450,9 @@
   </si>
   <si>
     <t>Gun sprite</t>
+  </si>
+  <si>
+    <t>Clipped Spr</t>
   </si>
 </sst>
 </file>
@@ -15071,14 +15074,15 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB40D263-C04C-4263-859C-02DFCB83777C}">
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.140625" style="4"/>
+    <col min="7" max="7" width="9.140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>45</v>
       </c>
@@ -15089,7 +15093,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>39</v>
       </c>
@@ -15105,7 +15109,7 @@
         <v>1.0833333333333333</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>46</v>
       </c>
@@ -15121,11 +15125,11 @@
         <v>3.5</v>
       </c>
       <c r="F3">
-        <f t="shared" ref="F3:F14" si="2">E3/3</f>
+        <f t="shared" ref="F3:F15" si="2">E3/3</f>
         <v>1.1666666666666667</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>47</v>
       </c>
@@ -15145,7 +15149,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>48</v>
       </c>
@@ -15165,7 +15169,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>49</v>
       </c>
@@ -15185,7 +15189,7 @@
         <v>5.25</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>51</v>
       </c>
@@ -15205,7 +15209,7 @@
         <v>3.4166666666666665</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>52</v>
       </c>
@@ -15225,7 +15229,7 @@
         <v>4.416666666666667</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>52</v>
       </c>
@@ -15245,7 +15249,7 @@
         <v>4.75</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>99</v>
       </c>
@@ -15265,7 +15269,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>100</v>
       </c>
@@ -15285,7 +15289,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>117</v>
       </c>
@@ -15305,7 +15309,7 @@
         <v>5.083333333333333</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>133</v>
       </c>
@@ -15317,7 +15321,7 @@
         <v>2.6666666666666665</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>52</v>
       </c>
@@ -15327,6 +15331,26 @@
       <c r="F14">
         <f t="shared" si="2"/>
         <v>3.6666666666666665</v>
+      </c>
+      <c r="G14" s="4">
+        <f>E14/E13</f>
+        <v>1.375</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>134</v>
+      </c>
+      <c r="E15">
+        <v>12</v>
+      </c>
+      <c r="F15">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="G15" s="4">
+        <f>E15/E14</f>
+        <v>1.0909090909090908</v>
       </c>
     </row>
   </sheetData>

--- a/Psion Levels.xlsx
+++ b/Psion Levels.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Zak\Documents\GitProjects\psion3d\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9905EA7A-F998-4A46-BFEF-D3F687D7BECB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A6E1940-096B-4EC5-9CA2-41A85899B772}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="5" activeTab="7" xr2:uid="{72A343FB-71F0-4738-BBFF-B23B40D170FF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{72A343FB-71F0-4738-BBFF-B23B40D170FF}"/>
   </bookViews>
   <sheets>
     <sheet name="Mapbits" sheetId="4" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4269" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4356" uniqueCount="154">
   <si>
     <t>X</t>
   </si>
@@ -454,6 +454,63 @@
   <si>
     <t>Clipped Spr</t>
   </si>
+  <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>J</t>
+  </si>
+  <si>
+    <t>K</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>O</t>
+  </si>
+  <si>
+    <t>Q</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>U</t>
+  </si>
+  <si>
+    <t>Z</t>
+  </si>
+  <si>
+    <t>MP5 Pickup</t>
+  </si>
+  <si>
+    <t>AK47 Pickup</t>
+  </si>
+  <si>
+    <t>M249 Pickup</t>
+  </si>
+  <si>
+    <t>? Pickup</t>
+  </si>
+  <si>
+    <t>Keycard Pickup</t>
+  </si>
+  <si>
+    <t>Locked Door</t>
+  </si>
+  <si>
+    <t>Pickups</t>
+  </si>
 </sst>
 </file>
 
@@ -490,12 +547,18 @@
       <family val="3"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -510,7 +573,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -530,11 +593,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="21">
     <dxf>
       <fill>
         <patternFill>
@@ -556,6 +620,107 @@
       <fill>
         <patternFill>
           <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFF00"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="1"/>
         </patternFill>
       </fill>
     </dxf>
@@ -956,7 +1121,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A21D89A8-E5EC-4EAA-92CE-B056DD4B8657}">
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:Q17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.5703125" bestFit="1" customWidth="1"/>
@@ -970,9 +1135,10 @@
     <col min="9" max="9" width="14.140625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>32</v>
       </c>
@@ -1000,8 +1166,17 @@
       <c r="M1" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="O1" t="s">
+        <v>153</v>
+      </c>
+      <c r="P1">
+        <v>0</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>15</v>
       </c>
@@ -1026,8 +1201,14 @@
       <c r="M2" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="P2">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>14</v>
       </c>
@@ -1052,8 +1233,14 @@
       <c r="M3" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="P3">
+        <v>2</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>13</v>
       </c>
@@ -1078,8 +1265,14 @@
       <c r="M4" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="P4">
+        <v>3</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>12</v>
       </c>
@@ -1101,8 +1294,11 @@
       <c r="L5">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="P5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>11</v>
       </c>
@@ -1124,8 +1320,11 @@
       <c r="L6">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="P6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>10</v>
       </c>
@@ -1147,8 +1346,11 @@
       <c r="L7">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="P7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>9</v>
       </c>
@@ -1167,8 +1369,11 @@
       <c r="L8">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="P8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1176,11 +1381,20 @@
       <c r="G9">
         <v>8</v>
       </c>
+      <c r="H9" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="I9" t="s">
+        <v>152</v>
+      </c>
       <c r="L9">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="P9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>7</v>
       </c>
@@ -1192,8 +1406,11 @@
       <c r="L10">
         <v>9</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="P10">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>6</v>
       </c>
@@ -1205,8 +1422,11 @@
       <c r="L11">
         <v>10</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="P11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>5</v>
       </c>
@@ -1220,8 +1440,11 @@
       <c r="L12">
         <v>11</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="P12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>4</v>
       </c>
@@ -1233,8 +1456,11 @@
       <c r="L13">
         <v>12</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="P13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>3</v>
       </c>
@@ -1246,8 +1472,11 @@
       <c r="L14">
         <v>13</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="P14">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2</v>
       </c>
@@ -1259,8 +1488,11 @@
       <c r="L15">
         <v>14</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="P15">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>1</v>
       </c>
@@ -1270,6 +1502,9 @@
         <v>15</v>
       </c>
       <c r="L16">
+        <v>15</v>
+      </c>
+      <c r="P16">
         <v>15</v>
       </c>
     </row>
@@ -1846,14 +2081,15 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3F90467-4CD9-40FD-80C5-3B27CEDF7551}">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="2.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>6</v>
       </c>
@@ -1875,8 +2111,11 @@
       <c r="G1" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="M1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>0</v>
       </c>
@@ -1898,8 +2137,11 @@
       <c r="G2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="M2" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
@@ -1921,8 +2163,11 @@
       <c r="G3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="M3" s="11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
@@ -1944,8 +2189,11 @@
       <c r="G4" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="M4" s="11" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>1</v>
       </c>
@@ -1967,8 +2215,11 @@
       <c r="G5" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="M5" s="11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>2</v>
       </c>
@@ -1990,8 +2241,11 @@
       <c r="G6" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="M6" s="11" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>3</v>
       </c>
@@ -2013,22 +2267,25 @@
       <c r="G7" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="M7" s="11" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>5</v>
+        <v>144</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>152</v>
       </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D8" t="s">
         <v>25</v>
       </c>
       <c r="E8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F8" t="s">
         <v>24</v>
@@ -2036,22 +2293,25 @@
       <c r="G8" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="M8" s="11" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D9" t="s">
         <v>25</v>
       </c>
       <c r="E9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F9" t="s">
         <v>24</v>
@@ -2059,16 +2319,19 @@
       <c r="G9" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="M9" s="11" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D10" t="s">
         <v>25</v>
@@ -2082,36 +2345,47 @@
       <c r="G10" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
+      <c r="M10" s="11" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" t="s">
+        <v>24</v>
+      </c>
+      <c r="F11" t="s">
+        <v>24</v>
+      </c>
+      <c r="G11" t="s">
+        <v>24</v>
+      </c>
+      <c r="M11" s="11" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M12" s="11" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B13" t="s">
         <v>90</v>
-      </c>
-      <c r="C12" t="s">
-        <v>24</v>
-      </c>
-      <c r="D12" t="s">
-        <v>24</v>
-      </c>
-      <c r="E12" t="s">
-        <v>25</v>
-      </c>
-      <c r="F12" t="s">
-        <v>25</v>
-      </c>
-      <c r="G12" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B13" t="s">
-        <v>91</v>
       </c>
       <c r="C13" t="s">
         <v>24</v>
@@ -2128,13 +2402,16 @@
       <c r="G13" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="M13" s="11" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B14" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C14" t="s">
         <v>24</v>
@@ -2151,13 +2428,16 @@
       <c r="G14" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="M14" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="B15" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="C15" t="s">
         <v>24</v>
@@ -2173,6 +2453,303 @@
       </c>
       <c r="G15" t="s">
         <v>25</v>
+      </c>
+      <c r="M15" s="11" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" t="s">
+        <v>61</v>
+      </c>
+      <c r="C16" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16" t="s">
+        <v>25</v>
+      </c>
+      <c r="F16" t="s">
+        <v>25</v>
+      </c>
+      <c r="G16" t="s">
+        <v>25</v>
+      </c>
+      <c r="M16" s="11" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M17" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B18" t="s">
+        <v>147</v>
+      </c>
+      <c r="C18" t="s">
+        <v>24</v>
+      </c>
+      <c r="D18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E18" t="s">
+        <v>25</v>
+      </c>
+      <c r="F18" t="s">
+        <v>25</v>
+      </c>
+      <c r="G18" t="s">
+        <v>24</v>
+      </c>
+      <c r="M18" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B19" t="s">
+        <v>148</v>
+      </c>
+      <c r="C19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D19" t="s">
+        <v>24</v>
+      </c>
+      <c r="E19" t="s">
+        <v>25</v>
+      </c>
+      <c r="F19" t="s">
+        <v>25</v>
+      </c>
+      <c r="G19" t="s">
+        <v>24</v>
+      </c>
+      <c r="M19" s="11" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B20" t="s">
+        <v>149</v>
+      </c>
+      <c r="C20" t="s">
+        <v>24</v>
+      </c>
+      <c r="D20" t="s">
+        <v>24</v>
+      </c>
+      <c r="E20" t="s">
+        <v>25</v>
+      </c>
+      <c r="F20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G20" t="s">
+        <v>24</v>
+      </c>
+      <c r="M20" s="11" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B21" t="s">
+        <v>151</v>
+      </c>
+      <c r="C21" t="s">
+        <v>24</v>
+      </c>
+      <c r="D21" t="s">
+        <v>24</v>
+      </c>
+      <c r="E21" t="s">
+        <v>25</v>
+      </c>
+      <c r="F21" t="s">
+        <v>25</v>
+      </c>
+      <c r="G21" t="s">
+        <v>24</v>
+      </c>
+      <c r="M21" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B22" t="s">
+        <v>150</v>
+      </c>
+      <c r="C22" t="s">
+        <v>24</v>
+      </c>
+      <c r="D22" t="s">
+        <v>24</v>
+      </c>
+      <c r="E22" t="s">
+        <v>25</v>
+      </c>
+      <c r="F22" t="s">
+        <v>25</v>
+      </c>
+      <c r="G22" t="s">
+        <v>24</v>
+      </c>
+      <c r="M22" s="11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B23" t="s">
+        <v>150</v>
+      </c>
+      <c r="C23" t="s">
+        <v>24</v>
+      </c>
+      <c r="D23" t="s">
+        <v>24</v>
+      </c>
+      <c r="E23" t="s">
+        <v>25</v>
+      </c>
+      <c r="F23" t="s">
+        <v>25</v>
+      </c>
+      <c r="G23" t="s">
+        <v>24</v>
+      </c>
+      <c r="M23" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24" t="s">
+        <v>150</v>
+      </c>
+      <c r="C24" t="s">
+        <v>24</v>
+      </c>
+      <c r="D24" t="s">
+        <v>24</v>
+      </c>
+      <c r="E24" t="s">
+        <v>25</v>
+      </c>
+      <c r="F24" t="s">
+        <v>25</v>
+      </c>
+      <c r="G24" t="s">
+        <v>24</v>
+      </c>
+      <c r="M24" s="11" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B25" t="s">
+        <v>150</v>
+      </c>
+      <c r="C25" t="s">
+        <v>24</v>
+      </c>
+      <c r="D25" t="s">
+        <v>24</v>
+      </c>
+      <c r="E25" t="s">
+        <v>25</v>
+      </c>
+      <c r="F25" t="s">
+        <v>25</v>
+      </c>
+      <c r="G25" t="s">
+        <v>24</v>
+      </c>
+      <c r="M25" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M26" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M27" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M29">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M30">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M31">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M32">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="13:13" x14ac:dyDescent="0.25">
+      <c r="M33">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="13:13" x14ac:dyDescent="0.25">
+      <c r="M34">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="13:13" x14ac:dyDescent="0.25">
+      <c r="M35">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36" spans="13:13" x14ac:dyDescent="0.25">
+      <c r="M36">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -4880,7 +5457,7 @@
         <v>0</v>
       </c>
       <c r="X14" s="2" t="s">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="Y14" s="2" t="s">
         <v>0</v>
@@ -5004,7 +5581,7 @@
       </c>
       <c r="BM14" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
+        <v>XXXXXXXXXXXXXXXXXXXXXXXTXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
     </row>
     <row r="15" spans="1:65" x14ac:dyDescent="0.25">
@@ -5074,13 +5651,13 @@
       <c r="V15" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="W15" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="X15" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="2" t="s">
+      <c r="W15" s="2">
+        <v>0</v>
+      </c>
+      <c r="X15" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="2">
         <v>0</v>
       </c>
       <c r="Z15" s="2" t="s">
@@ -5202,7 +5779,7 @@
       </c>
       <c r="BM15" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
+        <v>XXXXXXXXXXXXXXXXXXXXXX000XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
     </row>
     <row r="16" spans="1:65" x14ac:dyDescent="0.25">
@@ -5272,13 +5849,13 @@
       <c r="V16" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="W16" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="X16" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="Y16" s="2" t="s">
+      <c r="W16" s="2">
+        <v>0</v>
+      </c>
+      <c r="X16" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="2">
         <v>0</v>
       </c>
       <c r="Z16" s="2" t="s">
@@ -5400,7 +5977,7 @@
       </c>
       <c r="BM16" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
+        <v>XXXXXXXXXXXXXXXXXXXXXX000XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
     </row>
     <row r="17" spans="1:65" x14ac:dyDescent="0.25">
@@ -5470,13 +6047,13 @@
       <c r="V17" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="W17" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="X17" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="Y17" s="2" t="s">
+      <c r="W17" s="2">
+        <v>0</v>
+      </c>
+      <c r="X17" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="2">
         <v>0</v>
       </c>
       <c r="Z17" s="2" t="s">
@@ -5598,7 +6175,7 @@
       </c>
       <c r="BM17" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
+        <v>XXXXXXXXXXXXXXXXXXXXXX000XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
     </row>
     <row r="18" spans="1:65" x14ac:dyDescent="0.25">
@@ -14909,37 +15486,40 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:BL64">
-    <cfRule type="containsText" dxfId="9" priority="11" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="20" priority="12" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH("X",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:BL1048576">
-    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="2" operator="equal">
       <formula>"G"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="3" operator="equal">
       <formula>"F"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="4" operator="equal">
       <formula>"E"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="6" operator="equal">
       <formula>"B"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="7" operator="equal">
       <formula>"C"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="8" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="8" operator="equal">
-      <formula>"D"</formula>
+    <cfRule type="cellIs" dxfId="10" priority="9" operator="equal">
+      <formula>"T"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="10" operator="equal">
       <formula>"P"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="11" operator="equal">
       <formula>"W"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
+      <formula>"D"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Psion Levels.xlsx
+++ b/Psion Levels.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Zak\Documents\GitProjects\psion3d\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A6E1940-096B-4EC5-9CA2-41A85899B772}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C4597E5-22BA-410B-B00C-7C7B7FF13FF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{72A343FB-71F0-4738-BBFF-B23B40D170FF}"/>
   </bookViews>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4356" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4357" uniqueCount="154">
   <si>
     <t>X</t>
   </si>
@@ -5060,8 +5060,8 @@
       <c r="W12" s="2">
         <v>0</v>
       </c>
-      <c r="X12" s="2">
-        <v>0</v>
+      <c r="X12" s="2" t="s">
+        <v>138</v>
       </c>
       <c r="Y12" s="2">
         <v>0</v>
@@ -5185,7 +5185,7 @@
       </c>
       <c r="BM12" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>XXXXXXXXXXXXXXXXXXXXXX000W0P0XXXXX0XXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
+        <v>XXXXXXXXXXXXXXXXXXXXXX0K0W0P0XXXXX0XXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
     </row>
     <row r="13" spans="1:65" x14ac:dyDescent="0.25">

--- a/Psion Levels.xlsx
+++ b/Psion Levels.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Zak\Documents\GitProjects\psion3d\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C4597E5-22BA-410B-B00C-7C7B7FF13FF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E5855B3-311B-49F3-9B79-9EC0927EA24A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{72A343FB-71F0-4738-BBFF-B23B40D170FF}"/>
   </bookViews>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4357" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4443" uniqueCount="179">
   <si>
     <t>X</t>
   </si>
@@ -332,15 +332,6 @@
     <t>Wall types</t>
   </si>
   <si>
-    <t>Default wall</t>
-  </si>
-  <si>
-    <t>Dark Wall</t>
-  </si>
-  <si>
-    <t>Bars</t>
-  </si>
-  <si>
     <t>Enemy Types</t>
   </si>
   <si>
@@ -510,6 +501,90 @@
   </si>
   <si>
     <t>Pickups</t>
+  </si>
+  <si>
+    <t>SOLID (default)</t>
+  </si>
+  <si>
+    <t>DARK</t>
+  </si>
+  <si>
+    <t>WINDOW</t>
+  </si>
+  <si>
+    <t>ARCH</t>
+  </si>
+  <si>
+    <t>UNLOCKED_DOOR</t>
+  </si>
+  <si>
+    <t>BARS</t>
+  </si>
+  <si>
+    <t>VOID</t>
+  </si>
+  <si>
+    <t>LOCKED_DOOR</t>
+  </si>
+  <si>
+    <t>!</t>
+  </si>
+  <si>
+    <t>SIGN</t>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
+    <t>LIGHT</t>
+  </si>
+  <si>
+    <t>:</t>
+  </si>
+  <si>
+    <t>PIPES</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>SHELF</t>
+  </si>
+  <si>
+    <t>LOW</t>
+  </si>
+  <si>
+    <t>|</t>
+  </si>
+  <si>
+    <t>PILLAR</t>
+  </si>
+  <si>
+    <t>SWITCH</t>
+  </si>
+  <si>
+    <t>SHOOTABLE</t>
+  </si>
+  <si>
+    <t>Decorations</t>
+  </si>
+  <si>
+    <t>Camera</t>
+  </si>
+  <si>
+    <t>Computer</t>
+  </si>
+  <si>
+    <t>Reserved</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Map</t>
+  </si>
+  <si>
+    <t>Item</t>
   </si>
 </sst>
 </file>
@@ -520,7 +595,7 @@
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -544,6 +619,21 @@
       <sz val="11"/>
       <color rgb="FF569CD6"/>
       <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Cascadia Code"/>
       <family val="3"/>
     </font>
   </fonts>
@@ -573,7 +663,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -590,15 +680,21 @@
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="21">
+  <dxfs count="11">
     <dxf>
       <fill>
         <patternFill>
@@ -617,9 +713,12 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
       <fill>
         <patternFill>
-          <bgColor theme="8" tint="0.59996337778862885"/>
+          <bgColor theme="8" tint="-0.24994659260841701"/>
         </patternFill>
       </fill>
     </dxf>
@@ -681,103 +780,9 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="8" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFF00"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1121,7 +1126,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A21D89A8-E5EC-4EAA-92CE-B056DD4B8657}">
-  <dimension ref="A1:Q17"/>
+  <dimension ref="A1:X17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.5703125" bestFit="1" customWidth="1"/>
@@ -1132,13 +1137,20 @@
     <col min="6" max="6" width="9.85546875" customWidth="1"/>
     <col min="7" max="7" width="11" customWidth="1"/>
     <col min="8" max="8" width="13" customWidth="1"/>
-    <col min="9" max="9" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.85546875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="2.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="3" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="2.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="3" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>32</v>
       </c>
@@ -1151,32 +1163,47 @@
       <c r="G1">
         <v>0</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" t="s">
         <v>0</v>
       </c>
       <c r="I1" t="s">
+        <v>151</v>
+      </c>
+      <c r="K1" t="s">
         <v>94</v>
       </c>
-      <c r="K1" t="s">
-        <v>97</v>
-      </c>
-      <c r="L1">
-        <v>0</v>
-      </c>
-      <c r="M1" t="s">
+      <c r="L1" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="M1">
+        <v>0</v>
+      </c>
+      <c r="N1" t="s">
         <v>61</v>
       </c>
-      <c r="O1" t="s">
-        <v>153</v>
-      </c>
-      <c r="P1">
-        <v>0</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="P1" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q1">
+        <v>0</v>
+      </c>
+      <c r="R1" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="S1" t="s">
+        <v>144</v>
+      </c>
+      <c r="V1" t="s">
+        <v>176</v>
+      </c>
+      <c r="W1" t="s">
+        <v>177</v>
+      </c>
+      <c r="X1" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>15</v>
       </c>
@@ -1189,26 +1216,44 @@
       <c r="G2">
         <v>1</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" t="s">
         <v>4</v>
       </c>
       <c r="I2" t="s">
-        <v>95</v>
-      </c>
-      <c r="L2">
+        <v>152</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="M2">
         <v>1</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>79</v>
       </c>
-      <c r="P2">
+      <c r="Q2">
         <v>1</v>
       </c>
-      <c r="Q2" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="R2" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="S2" t="s">
+        <v>145</v>
+      </c>
+      <c r="U2" t="s">
+        <v>172</v>
+      </c>
+      <c r="V2">
+        <v>0</v>
+      </c>
+      <c r="W2">
+        <v>1</v>
+      </c>
+      <c r="X2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>14</v>
       </c>
@@ -1221,26 +1266,41 @@
       <c r="G3">
         <v>2</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" t="s">
         <v>1</v>
       </c>
       <c r="I3" t="s">
-        <v>10</v>
-      </c>
-      <c r="L3">
+        <v>153</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="M3">
         <v>2</v>
       </c>
-      <c r="M3" t="s">
-        <v>98</v>
-      </c>
-      <c r="P3">
+      <c r="N3" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q3">
         <v>2</v>
       </c>
-      <c r="Q3" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="R3" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="S3" t="s">
+        <v>146</v>
+      </c>
+      <c r="V3">
+        <v>1</v>
+      </c>
+      <c r="W3">
+        <v>2</v>
+      </c>
+      <c r="X3" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>13</v>
       </c>
@@ -1253,26 +1313,41 @@
       <c r="G4">
         <v>3</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" t="s">
         <v>2</v>
       </c>
       <c r="I4" t="s">
-        <v>11</v>
-      </c>
-      <c r="L4">
+        <v>154</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="M4">
         <v>3</v>
       </c>
-      <c r="M4" t="s">
+      <c r="N4" t="s">
         <v>81</v>
       </c>
-      <c r="P4">
+      <c r="Q4">
         <v>3</v>
       </c>
-      <c r="Q4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="R4" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="S4" t="s">
+        <v>148</v>
+      </c>
+      <c r="V4">
+        <v>2</v>
+      </c>
+      <c r="W4">
+        <v>3</v>
+      </c>
+      <c r="X4" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>12</v>
       </c>
@@ -1285,20 +1360,32 @@
       <c r="G5">
         <v>4</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="H5" t="s">
         <v>3</v>
       </c>
       <c r="I5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L5">
+        <v>155</v>
+      </c>
+      <c r="M5">
         <v>4</v>
       </c>
-      <c r="P5">
+      <c r="Q5">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:17" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="R5" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="V5">
+        <v>3</v>
+      </c>
+      <c r="W5">
+        <v>4</v>
+      </c>
+      <c r="X5" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>11</v>
       </c>
@@ -1311,20 +1398,32 @@
       <c r="G6">
         <v>5</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="H6" t="s">
         <v>5</v>
       </c>
       <c r="I6" t="s">
-        <v>13</v>
-      </c>
-      <c r="L6">
+        <v>171</v>
+      </c>
+      <c r="M6">
         <v>5</v>
       </c>
-      <c r="P6">
+      <c r="Q6">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:17" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="R6" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="V6">
+        <v>4</v>
+      </c>
+      <c r="W6">
+        <v>5</v>
+      </c>
+      <c r="X6" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>10</v>
       </c>
@@ -1337,183 +1436,282 @@
       <c r="G7">
         <v>6</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="H7" t="s">
         <v>19</v>
       </c>
       <c r="I7" t="s">
-        <v>96</v>
-      </c>
-      <c r="L7">
+        <v>156</v>
+      </c>
+      <c r="M7">
         <v>6</v>
       </c>
-      <c r="P7">
+      <c r="Q7">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="R7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="V7">
+        <v>5</v>
+      </c>
+      <c r="W7">
+        <v>6</v>
+      </c>
+      <c r="X7" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>9</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="11" t="s">
         <v>6</v>
       </c>
       <c r="G8">
         <v>7</v>
       </c>
-      <c r="H8" s="3" t="s">
+      <c r="H8" t="s">
         <v>21</v>
       </c>
       <c r="I8" t="s">
-        <v>22</v>
-      </c>
-      <c r="L8">
+        <v>157</v>
+      </c>
+      <c r="M8">
         <v>7</v>
       </c>
-      <c r="P8">
+      <c r="Q8">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="R8" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="V8">
+        <v>6</v>
+      </c>
+      <c r="W8">
+        <v>7</v>
+      </c>
+      <c r="X8" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" s="10"/>
+      <c r="B9" s="11"/>
       <c r="G9">
         <v>8</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>144</v>
+      <c r="H9" t="s">
+        <v>141</v>
       </c>
       <c r="I9" t="s">
-        <v>152</v>
-      </c>
-      <c r="L9">
+        <v>158</v>
+      </c>
+      <c r="M9">
         <v>8</v>
       </c>
-      <c r="P9">
+      <c r="Q9">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="V9">
+        <v>7</v>
+      </c>
+      <c r="W9">
+        <v>8</v>
+      </c>
+      <c r="X9" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>7</v>
       </c>
-      <c r="B10" s="10"/>
+      <c r="B10" s="11"/>
       <c r="C10" s="6"/>
       <c r="G10">
         <v>9</v>
       </c>
-      <c r="L10">
+      <c r="H10" t="s">
+        <v>159</v>
+      </c>
+      <c r="I10" t="s">
+        <v>160</v>
+      </c>
+      <c r="M10">
         <v>9</v>
       </c>
-      <c r="P10">
+      <c r="Q10">
         <v>9</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="V10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>6</v>
       </c>
-      <c r="B11" s="10"/>
+      <c r="B11" s="11"/>
       <c r="C11" s="6"/>
       <c r="G11">
         <v>10</v>
       </c>
-      <c r="L11">
+      <c r="H11" t="s">
+        <v>161</v>
+      </c>
+      <c r="I11" t="s">
+        <v>162</v>
+      </c>
+      <c r="M11">
         <v>10</v>
       </c>
-      <c r="P11">
+      <c r="Q11">
         <v>10</v>
       </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="V11">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>5</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="11" t="s">
         <v>31</v>
       </c>
       <c r="C12" s="6"/>
       <c r="G12">
         <v>11</v>
       </c>
-      <c r="L12">
+      <c r="H12" t="s">
+        <v>163</v>
+      </c>
+      <c r="I12" t="s">
+        <v>164</v>
+      </c>
+      <c r="M12">
         <v>11</v>
       </c>
-      <c r="P12">
+      <c r="Q12">
         <v>11</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="V12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>4</v>
       </c>
-      <c r="B13" s="10"/>
+      <c r="B13" s="11"/>
       <c r="C13" s="6"/>
       <c r="G13">
         <v>12</v>
       </c>
-      <c r="L13">
+      <c r="H13" t="s">
+        <v>165</v>
+      </c>
+      <c r="I13" t="s">
+        <v>166</v>
+      </c>
+      <c r="M13">
         <v>12</v>
       </c>
-      <c r="P13">
+      <c r="Q13">
         <v>12</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="V13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>3</v>
       </c>
-      <c r="B14" s="10"/>
+      <c r="B14" s="11"/>
       <c r="C14" s="6"/>
       <c r="G14">
         <v>13</v>
       </c>
-      <c r="L14">
+      <c r="H14" t="s">
+        <v>140</v>
+      </c>
+      <c r="I14" t="s">
+        <v>167</v>
+      </c>
+      <c r="M14">
         <v>13</v>
       </c>
-      <c r="P14">
+      <c r="Q14">
         <v>13</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="V14">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2</v>
       </c>
-      <c r="B15" s="10"/>
+      <c r="B15" s="11"/>
       <c r="C15" s="6"/>
       <c r="G15">
         <v>14</v>
       </c>
-      <c r="L15">
+      <c r="H15" t="s">
+        <v>168</v>
+      </c>
+      <c r="I15" t="s">
+        <v>169</v>
+      </c>
+      <c r="M15">
         <v>14</v>
       </c>
-      <c r="P15">
+      <c r="Q15">
         <v>14</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="V15">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>1</v>
       </c>
-      <c r="B16" s="10"/>
+      <c r="B16" s="11"/>
       <c r="C16" s="6"/>
       <c r="G16">
         <v>15</v>
       </c>
-      <c r="L16">
+      <c r="H16" t="s">
+        <v>142</v>
+      </c>
+      <c r="I16" t="s">
+        <v>170</v>
+      </c>
+      <c r="M16">
         <v>15</v>
       </c>
-      <c r="P16">
+      <c r="Q16">
         <v>15</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="V16">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>0</v>
       </c>
-      <c r="B17" s="10"/>
+      <c r="B17" s="11"/>
       <c r="C17" s="6"/>
+      <c r="V17">
+        <v>15</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1538,32 +1736,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B1" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10" t="s">
+      <c r="B1" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="E1" s="10"/>
+      <c r="E1" s="11"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B3">
         <v>32000</v>
@@ -1582,7 +1780,7 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B4">
         <v>850</v>
@@ -1609,7 +1807,7 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B5">
         <v>29000</v>
@@ -1636,7 +1834,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B6">
         <v>32000</v>
@@ -1663,7 +1861,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B7">
         <v>32000</v>
@@ -1694,7 +1892,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B8">
         <v>2600</v>
@@ -1721,7 +1919,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B9">
         <v>2800</v>
@@ -1744,7 +1942,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B10">
         <v>3800</v>
@@ -1798,7 +1996,7 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D12">
         <v>9</v>
@@ -1814,7 +2012,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D13">
         <v>15</v>
@@ -1838,7 +2036,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D14">
         <v>8</v>
@@ -1850,7 +2048,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D15">
         <v>11</v>
@@ -1965,10 +2163,10 @@
         <v>82</v>
       </c>
       <c r="D3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -2013,13 +2211,13 @@
         <v>85</v>
       </c>
       <c r="D6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E6" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -2044,13 +2242,13 @@
         <v>76</v>
       </c>
       <c r="D8" t="s">
+        <v>102</v>
+      </c>
+      <c r="E8" t="s">
+        <v>103</v>
+      </c>
+      <c r="F8" t="s">
         <v>105</v>
-      </c>
-      <c r="E8" t="s">
-        <v>106</v>
-      </c>
-      <c r="F8" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -2061,13 +2259,13 @@
         <v>71</v>
       </c>
       <c r="D9" t="s">
+        <v>104</v>
+      </c>
+      <c r="E9" t="s">
+        <v>106</v>
+      </c>
+      <c r="F9" t="s">
         <v>107</v>
-      </c>
-      <c r="E9" t="s">
-        <v>109</v>
-      </c>
-      <c r="F9" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -2081,7 +2279,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3F90467-4CD9-40FD-80C5-3B27CEDF7551}">
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="3" bestFit="1" customWidth="1"/>
@@ -2137,7 +2335,7 @@
       <c r="G2" t="s">
         <v>24</v>
       </c>
-      <c r="M2" s="11" t="s">
+      <c r="M2" s="10" t="s">
         <v>19</v>
       </c>
     </row>
@@ -2163,7 +2361,7 @@
       <c r="G3" t="s">
         <v>24</v>
       </c>
-      <c r="M3" s="11" t="s">
+      <c r="M3" s="10" t="s">
         <v>45</v>
       </c>
     </row>
@@ -2189,7 +2387,7 @@
       <c r="G4" t="s">
         <v>24</v>
       </c>
-      <c r="M4" s="11" t="s">
+      <c r="M4" s="10" t="s">
         <v>3</v>
       </c>
     </row>
@@ -2215,7 +2413,7 @@
       <c r="G5" t="s">
         <v>24</v>
       </c>
-      <c r="M5" s="11" t="s">
+      <c r="M5" s="10" t="s">
         <v>58</v>
       </c>
     </row>
@@ -2241,7 +2439,7 @@
       <c r="G6" t="s">
         <v>24</v>
       </c>
-      <c r="M6" s="11" t="s">
+      <c r="M6" s="10" t="s">
         <v>59</v>
       </c>
     </row>
@@ -2267,16 +2465,16 @@
       <c r="G7" t="s">
         <v>24</v>
       </c>
-      <c r="M7" s="11" t="s">
+      <c r="M7" s="10" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B8" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C8" t="s">
         <v>24</v>
@@ -2293,8 +2491,8 @@
       <c r="G8" t="s">
         <v>24</v>
       </c>
-      <c r="M8" s="11" t="s">
-        <v>135</v>
+      <c r="M8" s="10" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
@@ -2311,7 +2509,7 @@
         <v>25</v>
       </c>
       <c r="E9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F9" t="s">
         <v>24</v>
@@ -2319,12 +2517,12 @@
       <c r="G9" t="s">
         <v>24</v>
       </c>
-      <c r="M9" s="11" t="s">
-        <v>136</v>
+      <c r="M9" s="10" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="12" t="s">
         <v>19</v>
       </c>
       <c r="B10" t="s">
@@ -2345,12 +2543,12 @@
       <c r="G10" t="s">
         <v>24</v>
       </c>
-      <c r="M10" s="11" t="s">
-        <v>137</v>
+      <c r="M10" s="10" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="12" t="s">
         <v>21</v>
       </c>
       <c r="B11" t="s">
@@ -2371,182 +2569,203 @@
       <c r="G11" t="s">
         <v>24</v>
       </c>
-      <c r="M11" s="11" t="s">
+      <c r="M11" s="10" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="B12" t="s">
+        <v>160</v>
+      </c>
+      <c r="C12" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" t="s">
+        <v>24</v>
+      </c>
+      <c r="F12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G12" t="s">
+        <v>24</v>
+      </c>
+      <c r="M12" s="10" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="A13" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="B13" t="s">
+        <v>162</v>
+      </c>
+      <c r="C13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D13" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" t="s">
+        <v>24</v>
+      </c>
+      <c r="F13" t="s">
+        <v>24</v>
+      </c>
+      <c r="G13" t="s">
+        <v>24</v>
+      </c>
+      <c r="M13" s="10" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="B14" t="s">
+        <v>164</v>
+      </c>
+      <c r="C14" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" t="s">
+        <v>24</v>
+      </c>
+      <c r="F14" t="s">
+        <v>24</v>
+      </c>
+      <c r="G14" t="s">
+        <v>24</v>
+      </c>
+      <c r="M14" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="A15" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="B15" t="s">
+        <v>166</v>
+      </c>
+      <c r="C15" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" t="s">
+        <v>24</v>
+      </c>
+      <c r="F15" t="s">
+        <v>24</v>
+      </c>
+      <c r="G15" t="s">
+        <v>24</v>
+      </c>
+      <c r="M15" s="10" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="M12" s="11" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="B13" t="s">
-        <v>90</v>
-      </c>
-      <c r="C13" t="s">
-        <v>24</v>
-      </c>
-      <c r="D13" t="s">
-        <v>24</v>
-      </c>
-      <c r="E13" t="s">
-        <v>25</v>
-      </c>
-      <c r="F13" t="s">
-        <v>25</v>
-      </c>
-      <c r="G13" t="s">
-        <v>25</v>
-      </c>
-      <c r="M13" s="11" t="s">
+    <row r="16" spans="1:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="A16" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B14" t="s">
-        <v>91</v>
-      </c>
-      <c r="C14" t="s">
-        <v>24</v>
-      </c>
-      <c r="D14" t="s">
-        <v>24</v>
-      </c>
-      <c r="E14" t="s">
-        <v>25</v>
-      </c>
-      <c r="F14" t="s">
-        <v>25</v>
-      </c>
-      <c r="G14" t="s">
-        <v>25</v>
-      </c>
-      <c r="M14" s="11" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B15" t="s">
-        <v>92</v>
-      </c>
-      <c r="C15" t="s">
-        <v>24</v>
-      </c>
-      <c r="D15" t="s">
-        <v>24</v>
-      </c>
-      <c r="E15" t="s">
-        <v>25</v>
-      </c>
-      <c r="F15" t="s">
-        <v>25</v>
-      </c>
-      <c r="G15" t="s">
-        <v>25</v>
-      </c>
-      <c r="M15" s="11" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
-        <v>45</v>
-      </c>
       <c r="B16" t="s">
-        <v>61</v>
+        <v>167</v>
       </c>
       <c r="C16" t="s">
         <v>24</v>
       </c>
       <c r="D16" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" t="s">
         <v>24</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
+        <v>24</v>
+      </c>
+      <c r="G16" t="s">
+        <v>24</v>
+      </c>
+      <c r="M16" s="10" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="A17" s="13" t="s">
+        <v>168</v>
+      </c>
+      <c r="B17" t="s">
+        <v>169</v>
+      </c>
+      <c r="C17" t="s">
+        <v>24</v>
+      </c>
+      <c r="D17" t="s">
         <v>25</v>
       </c>
-      <c r="F16" t="s">
+      <c r="E17" t="s">
+        <v>24</v>
+      </c>
+      <c r="F17" t="s">
+        <v>24</v>
+      </c>
+      <c r="G17" t="s">
+        <v>24</v>
+      </c>
+      <c r="M17" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="A18" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="B18" t="s">
+        <v>170</v>
+      </c>
+      <c r="C18" t="s">
         <v>25</v>
       </c>
-      <c r="G16" t="s">
+      <c r="D18" t="s">
         <v>25</v>
       </c>
-      <c r="M16" s="11" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="M17" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="B18" t="s">
-        <v>147</v>
-      </c>
-      <c r="C18" t="s">
+      <c r="E18" t="s">
         <v>24</v>
       </c>
-      <c r="D18" t="s">
+      <c r="F18" t="s">
         <v>24</v>
-      </c>
-      <c r="E18" t="s">
-        <v>25</v>
-      </c>
-      <c r="F18" t="s">
-        <v>25</v>
       </c>
       <c r="G18" t="s">
         <v>24</v>
       </c>
       <c r="M18" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="B19" t="s">
-        <v>148</v>
-      </c>
-      <c r="C19" t="s">
-        <v>24</v>
-      </c>
-      <c r="D19" t="s">
-        <v>24</v>
-      </c>
-      <c r="E19" t="s">
-        <v>25</v>
-      </c>
-      <c r="F19" t="s">
-        <v>25</v>
-      </c>
-      <c r="G19" t="s">
-        <v>24</v>
-      </c>
-      <c r="M19" s="11" t="s">
+      <c r="M19" s="10" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>137</v>
+        <v>58</v>
       </c>
       <c r="B20" t="s">
-        <v>149</v>
+        <v>90</v>
       </c>
       <c r="C20" t="s">
         <v>24</v>
@@ -2561,18 +2780,18 @@
         <v>25</v>
       </c>
       <c r="G20" t="s">
-        <v>24</v>
-      </c>
-      <c r="M20" s="11" t="s">
-        <v>144</v>
+        <v>25</v>
+      </c>
+      <c r="M20" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>138</v>
+        <v>59</v>
       </c>
       <c r="B21" t="s">
-        <v>151</v>
+        <v>91</v>
       </c>
       <c r="C21" t="s">
         <v>24</v>
@@ -2587,18 +2806,18 @@
         <v>25</v>
       </c>
       <c r="G21" t="s">
-        <v>24</v>
-      </c>
-      <c r="M21" t="s">
-        <v>145</v>
+        <v>25</v>
+      </c>
+      <c r="M21" s="10" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>139</v>
+        <v>60</v>
       </c>
       <c r="B22" t="s">
-        <v>150</v>
+        <v>92</v>
       </c>
       <c r="C22" t="s">
         <v>24</v>
@@ -2613,18 +2832,18 @@
         <v>25</v>
       </c>
       <c r="G22" t="s">
-        <v>24</v>
-      </c>
-      <c r="M22" s="11" t="s">
-        <v>21</v>
+        <v>25</v>
+      </c>
+      <c r="M22" s="10" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>140</v>
+        <v>45</v>
       </c>
       <c r="B23" t="s">
-        <v>150</v>
+        <v>61</v>
       </c>
       <c r="C23" t="s">
         <v>24</v>
@@ -2639,44 +2858,23 @@
         <v>25</v>
       </c>
       <c r="G23" t="s">
-        <v>24</v>
-      </c>
-      <c r="M23" s="11" t="s">
-        <v>1</v>
+        <v>25</v>
+      </c>
+      <c r="M23" s="10" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B24" t="s">
-        <v>150</v>
-      </c>
-      <c r="C24" t="s">
-        <v>24</v>
-      </c>
-      <c r="D24" t="s">
-        <v>24</v>
-      </c>
-      <c r="E24" t="s">
+      <c r="M24" t="s">
         <v>25</v>
-      </c>
-      <c r="F24" t="s">
-        <v>25</v>
-      </c>
-      <c r="G24" t="s">
-        <v>24</v>
-      </c>
-      <c r="M24" s="11" t="s">
-        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="B25" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="C25" t="s">
         <v>24</v>
@@ -2694,63 +2892,228 @@
         <v>24</v>
       </c>
       <c r="M25" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B26" t="s">
+        <v>145</v>
+      </c>
+      <c r="C26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D26" t="s">
+        <v>24</v>
+      </c>
+      <c r="E26" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="M26" t="s">
+      <c r="F26" t="s">
+        <v>25</v>
+      </c>
+      <c r="G26" t="s">
+        <v>24</v>
+      </c>
+      <c r="M26" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B27" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="M27" s="11">
-        <v>0</v>
+      <c r="C27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D27" t="s">
+        <v>24</v>
+      </c>
+      <c r="E27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F27" t="s">
+        <v>25</v>
+      </c>
+      <c r="G27" t="s">
+        <v>24</v>
+      </c>
+      <c r="M27">
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B28" t="s">
+        <v>148</v>
+      </c>
+      <c r="C28" t="s">
+        <v>24</v>
+      </c>
+      <c r="D28" t="s">
+        <v>24</v>
+      </c>
+      <c r="E28" t="s">
+        <v>25</v>
+      </c>
+      <c r="F28" t="s">
+        <v>25</v>
+      </c>
+      <c r="G28" t="s">
+        <v>24</v>
+      </c>
       <c r="M28">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B29" t="s">
+        <v>147</v>
+      </c>
+      <c r="C29" t="s">
+        <v>24</v>
+      </c>
+      <c r="D29" t="s">
+        <v>24</v>
+      </c>
+      <c r="E29" t="s">
+        <v>25</v>
+      </c>
+      <c r="F29" t="s">
+        <v>25</v>
+      </c>
+      <c r="G29" t="s">
+        <v>24</v>
+      </c>
       <c r="M29">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B30" t="s">
+        <v>147</v>
+      </c>
+      <c r="C30" t="s">
+        <v>24</v>
+      </c>
+      <c r="D30" t="s">
+        <v>24</v>
+      </c>
+      <c r="E30" t="s">
+        <v>25</v>
+      </c>
+      <c r="F30" t="s">
+        <v>25</v>
+      </c>
+      <c r="G30" t="s">
+        <v>24</v>
+      </c>
       <c r="M30">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A31" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B31" t="s">
+        <v>147</v>
+      </c>
+      <c r="C31" t="s">
+        <v>24</v>
+      </c>
+      <c r="D31" t="s">
+        <v>24</v>
+      </c>
+      <c r="E31" t="s">
+        <v>25</v>
+      </c>
+      <c r="F31" t="s">
+        <v>25</v>
+      </c>
+      <c r="G31" t="s">
+        <v>24</v>
+      </c>
       <c r="M31">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B32" t="s">
+        <v>147</v>
+      </c>
+      <c r="C32" t="s">
+        <v>24</v>
+      </c>
+      <c r="D32" t="s">
+        <v>24</v>
+      </c>
+      <c r="E32" t="s">
+        <v>25</v>
+      </c>
+      <c r="F32" t="s">
+        <v>25</v>
+      </c>
+      <c r="G32" t="s">
+        <v>24</v>
+      </c>
       <c r="M32">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="33" spans="13:13" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="M33">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="13:13" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="A34"/>
       <c r="M34">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="35" spans="13:13" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="A35"/>
       <c r="M35">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="36" spans="13:13" x14ac:dyDescent="0.25">
-      <c r="M36">
         <v>9</v>
       </c>
+    </row>
+    <row r="36" spans="1:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="A36"/>
+    </row>
+    <row r="37" spans="1:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="A37"/>
+    </row>
+    <row r="38" spans="1:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="A38"/>
+    </row>
+    <row r="39" spans="1:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="A39"/>
+    </row>
+    <row r="40" spans="1:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="A40"/>
+    </row>
+    <row r="41" spans="1:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="A41"/>
+    </row>
+    <row r="42" spans="1:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="A42"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2768,15 +3131,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B2" t="s">
         <v>79</v>
@@ -2784,15 +3147,15 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B3" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B4" t="s">
         <v>81</v>
@@ -4077,7 +4440,7 @@
         <v>0</v>
       </c>
       <c r="Z7" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA7" s="2">
         <v>0</v>
@@ -4089,7 +4452,7 @@
         <v>0</v>
       </c>
       <c r="AD7" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE7" s="2" t="s">
         <v>0</v>
@@ -4195,7 +4558,7 @@
       </c>
       <c r="BM7" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>XXXXXXXXXXXXXXXXXXXXXX0XX00G00XXXX0XXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
+        <v>XXXXXXXXXXXXXXXXXXXXXX0XX10G02XXXX0XXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
     </row>
     <row r="8" spans="1:65" x14ac:dyDescent="0.25">
@@ -5061,7 +5424,7 @@
         <v>0</v>
       </c>
       <c r="X12" s="2" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="Y12" s="2">
         <v>0</v>
@@ -5457,7 +5820,7 @@
         <v>0</v>
       </c>
       <c r="X14" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="Y14" s="2" t="s">
         <v>0</v>
@@ -15486,40 +15849,40 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:BL64">
-    <cfRule type="containsText" dxfId="20" priority="12" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="10" priority="12" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH("X",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:BL1048576">
-    <cfRule type="cellIs" dxfId="19" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
+      <formula>"D"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="8" priority="2" operator="equal">
       <formula>"G"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="3" operator="equal">
       <formula>"F"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="4" operator="equal">
       <formula>"E"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
       <formula>"B"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="7" operator="equal">
       <formula>"C"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="8" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="9" operator="equal">
       <formula>"T"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="10" operator="equal">
       <formula>"P"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="11" operator="equal">
       <formula>"W"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
-      <formula>"D"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15831,7 +16194,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B10">
         <v>600</v>
@@ -15851,7 +16214,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B11">
         <v>600</v>
@@ -15871,7 +16234,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B12">
         <v>610</v>
@@ -15891,7 +16254,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="E13">
         <v>8</v>
@@ -15919,7 +16282,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E15">
         <v>12</v>

--- a/Psion Levels.xlsx
+++ b/Psion Levels.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Zak\Documents\GitProjects\psion3d\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E5855B3-311B-49F3-9B79-9EC0927EA24A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8023281-1A43-4302-9472-7F3047DDEC4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{72A343FB-71F0-4738-BBFF-B23B40D170FF}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="21060" windowHeight="15585" activeTab="5" xr2:uid="{72A343FB-71F0-4738-BBFF-B23B40D170FF}"/>
   </bookViews>
   <sheets>
     <sheet name="Mapbits" sheetId="4" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4443" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4411" uniqueCount="179">
   <si>
     <t>X</t>
   </si>
@@ -681,14 +681,14 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1465,7 +1465,7 @@
       <c r="A8">
         <v>9</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="13" t="s">
         <v>6</v>
       </c>
       <c r="G8">
@@ -1500,7 +1500,7 @@
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" s="11"/>
+      <c r="B9" s="13"/>
       <c r="G9">
         <v>8</v>
       </c>
@@ -1530,7 +1530,7 @@
       <c r="A10">
         <v>7</v>
       </c>
-      <c r="B10" s="11"/>
+      <c r="B10" s="13"/>
       <c r="C10" s="6"/>
       <c r="G10">
         <v>9</v>
@@ -1555,7 +1555,7 @@
       <c r="A11">
         <v>6</v>
       </c>
-      <c r="B11" s="11"/>
+      <c r="B11" s="13"/>
       <c r="C11" s="6"/>
       <c r="G11">
         <v>10</v>
@@ -1580,7 +1580,7 @@
       <c r="A12">
         <v>5</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="13" t="s">
         <v>31</v>
       </c>
       <c r="C12" s="6"/>
@@ -1607,7 +1607,7 @@
       <c r="A13">
         <v>4</v>
       </c>
-      <c r="B13" s="11"/>
+      <c r="B13" s="13"/>
       <c r="C13" s="6"/>
       <c r="G13">
         <v>12</v>
@@ -1632,7 +1632,7 @@
       <c r="A14">
         <v>3</v>
       </c>
-      <c r="B14" s="11"/>
+      <c r="B14" s="13"/>
       <c r="C14" s="6"/>
       <c r="G14">
         <v>13</v>
@@ -1657,7 +1657,7 @@
       <c r="A15">
         <v>2</v>
       </c>
-      <c r="B15" s="11"/>
+      <c r="B15" s="13"/>
       <c r="C15" s="6"/>
       <c r="G15">
         <v>14</v>
@@ -1682,7 +1682,7 @@
       <c r="A16">
         <v>1</v>
       </c>
-      <c r="B16" s="11"/>
+      <c r="B16" s="13"/>
       <c r="C16" s="6"/>
       <c r="G16">
         <v>15</v>
@@ -1707,7 +1707,7 @@
       <c r="A17">
         <v>0</v>
       </c>
-      <c r="B17" s="11"/>
+      <c r="B17" s="13"/>
       <c r="C17" s="6"/>
       <c r="V17">
         <v>15</v>
@@ -1736,14 +1736,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11" t="s">
+      <c r="C1" s="13"/>
+      <c r="D1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="E1" s="11"/>
+      <c r="E1" s="13"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
@@ -2522,7 +2522,7 @@
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="11" t="s">
         <v>19</v>
       </c>
       <c r="B10" t="s">
@@ -2548,7 +2548,7 @@
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="12" t="s">
+      <c r="A11" s="11" t="s">
         <v>21</v>
       </c>
       <c r="B11" t="s">
@@ -2574,7 +2574,7 @@
       </c>
     </row>
     <row r="12" spans="1:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="A12" s="13" t="s">
+      <c r="A12" s="12" t="s">
         <v>159</v>
       </c>
       <c r="B12" t="s">
@@ -2587,7 +2587,7 @@
         <v>25</v>
       </c>
       <c r="E12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F12" t="s">
         <v>24</v>
@@ -2600,7 +2600,7 @@
       </c>
     </row>
     <row r="13" spans="1:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="12" t="s">
         <v>161</v>
       </c>
       <c r="B13" t="s">
@@ -2613,7 +2613,7 @@
         <v>25</v>
       </c>
       <c r="E13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F13" t="s">
         <v>24</v>
@@ -2626,7 +2626,7 @@
       </c>
     </row>
     <row r="14" spans="1:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="A14" s="13" t="s">
+      <c r="A14" s="12" t="s">
         <v>163</v>
       </c>
       <c r="B14" t="s">
@@ -2639,7 +2639,7 @@
         <v>25</v>
       </c>
       <c r="E14" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F14" t="s">
         <v>24</v>
@@ -2652,7 +2652,7 @@
       </c>
     </row>
     <row r="15" spans="1:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="A15" s="13" t="s">
+      <c r="A15" s="12" t="s">
         <v>165</v>
       </c>
       <c r="B15" t="s">
@@ -2665,7 +2665,7 @@
         <v>25</v>
       </c>
       <c r="E15" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F15" t="s">
         <v>24</v>
@@ -2678,7 +2678,7 @@
       </c>
     </row>
     <row r="16" spans="1:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="A16" s="13" t="s">
+      <c r="A16" s="12" t="s">
         <v>140</v>
       </c>
       <c r="B16" t="s">
@@ -2704,7 +2704,7 @@
       </c>
     </row>
     <row r="17" spans="1:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="A17" s="13" t="s">
+      <c r="A17" s="12" t="s">
         <v>168</v>
       </c>
       <c r="B17" t="s">
@@ -2730,7 +2730,7 @@
       </c>
     </row>
     <row r="18" spans="1:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="A18" s="13" t="s">
+      <c r="A18" s="12" t="s">
         <v>142</v>
       </c>
       <c r="B18" t="s">
@@ -2743,7 +2743,7 @@
         <v>25</v>
       </c>
       <c r="E18" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F18" t="s">
         <v>24</v>
@@ -3401,58 +3401,58 @@
       <c r="I2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="J2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="S2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="T2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="U2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="V2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="W2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="X2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="Y2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="Z2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="AA2" s="2" t="s">
+      <c r="J2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K2" s="2">
+        <v>0</v>
+      </c>
+      <c r="L2" s="2">
+        <v>0</v>
+      </c>
+      <c r="M2" s="2">
+        <v>0</v>
+      </c>
+      <c r="N2" s="2">
+        <v>0</v>
+      </c>
+      <c r="O2" s="2">
+        <v>0</v>
+      </c>
+      <c r="P2" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="2">
+        <v>0</v>
+      </c>
+      <c r="R2" s="2">
+        <v>0</v>
+      </c>
+      <c r="S2" s="2">
+        <v>0</v>
+      </c>
+      <c r="T2" s="2">
+        <v>0</v>
+      </c>
+      <c r="U2" s="2">
+        <v>0</v>
+      </c>
+      <c r="V2" s="2">
+        <v>0</v>
+      </c>
+      <c r="W2" s="2">
+        <v>0</v>
+      </c>
+      <c r="X2" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z2" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA2" s="2">
         <v>0</v>
       </c>
       <c r="AB2" s="2">
@@ -3567,8 +3567,8 @@
         <v>0</v>
       </c>
       <c r="BM2" s="1" t="str">
-        <f t="shared" ref="BM2:BM64" si="0">_xlfn.TEXTJOIN("",TRUE,A2:BL2)</f>
-        <v>XXXXXXXXXXXXXXXXXXXXXXXXXXX0000D0C00A00A00XXXXXXXXXXXXXXXXXXXXXX</v>
+        <f>_xlfn.TEXTJOIN("",TRUE,A2:BL2)</f>
+        <v>XXXXXXXXXV000000000000000000000D0C00A00A00XXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
     </row>
     <row r="3" spans="1:65" x14ac:dyDescent="0.25">
@@ -3603,46 +3603,46 @@
         <v>0</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>0</v>
+        <v>142</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>0</v>
+        <v>163</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>0</v>
+        <v>161</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>0</v>
+        <v>159</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U3" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V3" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W3" s="2" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X3" s="2" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y3" s="2" t="s">
         <v>0</v>
@@ -3765,8 +3765,8 @@
         <v>0</v>
       </c>
       <c r="BM3" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>XXXXXXXXXXXXXXXXXXXXXXXXXXXAXBXXXSXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
+        <f t="shared" ref="BM3:BM64" si="0">_xlfn.TEXTJOIN("",TRUE,A3:BL3)</f>
+        <v>XXXXXXXXXXU|R#:*!BBSWWPPXXXAXBXXXSXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
     </row>
     <row r="4" spans="1:65" x14ac:dyDescent="0.25">
@@ -3800,49 +3800,49 @@
       <c r="J4" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="K4" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="O4" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="P4" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="R4" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="S4" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="T4" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="U4" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="V4" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="W4" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="X4" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="Y4" s="2" t="s">
+      <c r="K4" s="2">
+        <v>0</v>
+      </c>
+      <c r="L4" s="2">
+        <v>0</v>
+      </c>
+      <c r="M4" s="2">
+        <v>0</v>
+      </c>
+      <c r="N4" s="2">
+        <v>0</v>
+      </c>
+      <c r="O4" s="2">
+        <v>0</v>
+      </c>
+      <c r="P4" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="2">
+        <v>0</v>
+      </c>
+      <c r="R4" s="2">
+        <v>0</v>
+      </c>
+      <c r="S4" s="2">
+        <v>0</v>
+      </c>
+      <c r="T4" s="2">
+        <v>0</v>
+      </c>
+      <c r="U4" s="2">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2">
+        <v>0</v>
+      </c>
+      <c r="W4" s="2">
+        <v>0</v>
+      </c>
+      <c r="X4" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="2">
         <v>0</v>
       </c>
       <c r="Z4" s="2">
@@ -3964,7 +3964,7 @@
       </c>
       <c r="BM4" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>XXXXXXXXXXXXXXXXXXXXXXXXX00000XXX0XXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
+        <v>XXXXXXXXXX00000000000000000000XXX0XXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</v>
       </c>
     </row>
     <row r="5" spans="1:65" x14ac:dyDescent="0.25">
